--- a/Data/National Accounts/PSA-20HHSW_2018PSNA_Qrt.xlsx
+++ b/Data/National Accounts/PSA-20HHSW_2018PSNA_Qrt.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Shared drives\QNAP\NAP Dissemination\As of January 2026\Tables\Prelim Q4 2025\NAP Q1 2000 to Q4 2025\Qtr\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\Shared drives\QNAP\NAP Dissemination\As of April 2026\Tables\NAP Q1 2000 to Q4 2025\Qtr\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8600735D-6705-4544-AF77-3D31EC71889B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26062675-90B5-47FA-9744-0B240E5225FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="794" xr2:uid="{736930C2-BFBB-46C3-AE9E-AECFC8C3145D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="794" xr2:uid="{736930C2-BFBB-46C3-AE9E-AECFC8C3145D}"/>
   </bookViews>
   <sheets>
     <sheet name="HHSW" sheetId="20" r:id="rId1"/>
@@ -689,10 +689,10 @@
     <t>Table 21.7 Gross Value Added in Human Health and Social Work Activities, by Industry</t>
   </si>
   <si>
-    <t>As of January 2026</t>
+    <t>Q1 2000 to Q4 2025</t>
   </si>
   <si>
-    <t>Q1 2000 to Q4 2025</t>
+    <t>As of April 2026</t>
   </si>
 </sst>
 </file>
@@ -742,10 +742,12 @@
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
@@ -1229,7 +1231,7 @@
     </row>
     <row r="3" spans="1:179" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4" spans="1:179" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.2">
@@ -1242,7 +1244,7 @@
     </row>
     <row r="6" spans="1:179" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="7" spans="1:179" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.2">
@@ -2233,28 +2235,28 @@
         <v>52834.305464915291</v>
       </c>
       <c r="CT12" s="25">
-        <v>44247.194652957303</v>
+        <v>43920.911424325284</v>
       </c>
       <c r="CU12" s="25">
-        <v>26523.361152445057</v>
+        <v>26352.623388483866</v>
       </c>
       <c r="CV12" s="25">
-        <v>39534.741915232727</v>
+        <v>39649.132851161659</v>
       </c>
       <c r="CW12" s="25">
-        <v>61794.666412761602</v>
+        <v>62082.80917512111</v>
       </c>
       <c r="CX12" s="25">
-        <v>49671.783356549095</v>
+        <v>49305.498669517474</v>
       </c>
       <c r="CY12" s="25">
-        <v>30153.71394499658</v>
+        <v>29959.606657315249</v>
       </c>
       <c r="CZ12" s="25">
-        <v>48347.311102788153</v>
+        <v>48487.200574649476</v>
       </c>
       <c r="DA12" s="25">
-        <v>71651.01717031037</v>
+        <v>71123.550010637642</v>
       </c>
       <c r="DB12" s="20"/>
       <c r="DC12" s="20"/>
@@ -2624,28 +2626,28 @@
         <v>73591.188071996497</v>
       </c>
       <c r="CT13" s="25">
-        <v>67484.374979131535</v>
+        <v>67471.59019893418</v>
       </c>
       <c r="CU13" s="25">
-        <v>84964.024209853931</v>
+        <v>85131.661505645883</v>
       </c>
       <c r="CV13" s="25">
-        <v>87294.449930561255</v>
+        <v>87660.051281924127</v>
       </c>
       <c r="CW13" s="25">
-        <v>84769.739273087427</v>
+        <v>84838.724071052158</v>
       </c>
       <c r="CX13" s="25">
-        <v>79392.632207951712</v>
+        <v>79383.280638146694</v>
       </c>
       <c r="CY13" s="25">
-        <v>97378.606567305804</v>
+        <v>97376.372566172315</v>
       </c>
       <c r="CZ13" s="25">
-        <v>101460.94331870241</v>
+        <v>102214.64201592866</v>
       </c>
       <c r="DA13" s="25">
-        <v>98232.602628457331</v>
+        <v>99023.154657254374</v>
       </c>
       <c r="DB13" s="20"/>
       <c r="DC13" s="20"/>
@@ -3015,28 +3017,28 @@
         <v>10520.079326524889</v>
       </c>
       <c r="CT14" s="25">
-        <v>6734.3151934497955</v>
+        <v>6540.2992133964572</v>
       </c>
       <c r="CU14" s="25">
-        <v>4744.5200748292464</v>
+        <v>4606.8275174424143</v>
       </c>
       <c r="CV14" s="25">
-        <v>8309.4592597802657</v>
+        <v>8022.7239850467686</v>
       </c>
       <c r="CW14" s="25">
-        <v>11884.169787044739</v>
+        <v>11514.335453577001</v>
       </c>
       <c r="CX14" s="25">
-        <v>7311.504250536711</v>
+        <v>7097.9091224546664</v>
       </c>
       <c r="CY14" s="25">
-        <v>5230.7545698697568</v>
+        <v>5081.0559386923469</v>
       </c>
       <c r="CZ14" s="25">
-        <v>8728.1174752247844</v>
+        <v>8430.4297362518901</v>
       </c>
       <c r="DA14" s="25">
-        <v>13227.336769176725</v>
+        <v>12815.703195671689</v>
       </c>
       <c r="DB14" s="20"/>
       <c r="DC14" s="20"/>
@@ -3586,28 +3588,28 @@
         <v>136945.57286343668</v>
       </c>
       <c r="CT16" s="17">
-        <v>118465.88482553864</v>
+        <v>117932.80083665592</v>
       </c>
       <c r="CU16" s="17">
-        <v>116231.90543712823</v>
+        <v>116091.11241157218</v>
       </c>
       <c r="CV16" s="17">
-        <v>135138.65110557424</v>
+        <v>135331.90811813256</v>
       </c>
       <c r="CW16" s="17">
-        <v>158448.57547289378</v>
+        <v>158435.86869975025</v>
       </c>
       <c r="CX16" s="17">
-        <v>136375.91981503752</v>
+        <v>135786.68843011884</v>
       </c>
       <c r="CY16" s="17">
-        <v>132763.07508217214</v>
+        <v>132417.03516217991</v>
       </c>
       <c r="CZ16" s="17">
-        <v>158536.37189671534</v>
+        <v>159132.27232683002</v>
       </c>
       <c r="DA16" s="17">
-        <v>183110.95656794443</v>
+        <v>182962.40786356371</v>
       </c>
       <c r="DB16" s="20"/>
       <c r="DC16" s="20"/>
@@ -4480,7 +4482,7 @@
     </row>
     <row r="23" spans="1:179" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A23" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B23" s="4"/>
       <c r="C23" s="4"/>
@@ -4805,7 +4807,7 @@
     </row>
     <row r="26" spans="1:179" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A26" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B26" s="4"/>
       <c r="C26" s="4"/>
@@ -6004,28 +6006,28 @@
         <v>39666.256053218225</v>
       </c>
       <c r="CT32" s="25">
-        <v>38681.93726921198</v>
+        <v>38396.6928038638</v>
       </c>
       <c r="CU32" s="25">
-        <v>23356.743776618325</v>
+        <v>23206.390349930352</v>
       </c>
       <c r="CV32" s="25">
-        <v>33649.725083104844</v>
+        <v>33747.088145554088</v>
       </c>
       <c r="CW32" s="25">
-        <v>44756.07651122057</v>
+        <v>44964.769919033082</v>
       </c>
       <c r="CX32" s="25">
-        <v>41415.369320301841</v>
+        <v>41109.968254250023</v>
       </c>
       <c r="CY32" s="25">
-        <v>25281.995798757376</v>
+        <v>25119.249024711782</v>
       </c>
       <c r="CZ32" s="25">
-        <v>39098.376681295165</v>
+        <v>39211.505025764054</v>
       </c>
       <c r="DA32" s="25">
-        <v>49725.143744668523</v>
+        <v>49359.086410507116</v>
       </c>
       <c r="DB32" s="20"/>
       <c r="DC32" s="20"/>
@@ -6395,28 +6397,28 @@
         <v>56231.67042209916</v>
       </c>
       <c r="CT33" s="25">
-        <v>63006.605031274557</v>
+        <v>62994.668562650768</v>
       </c>
       <c r="CU33" s="25">
-        <v>72923.344758411884</v>
+        <v>73067.225332057744</v>
       </c>
       <c r="CV33" s="25">
-        <v>69118.193910832822</v>
+        <v>69407.67056275814</v>
       </c>
       <c r="CW33" s="25">
-        <v>62988.528629577348</v>
+        <v>63039.788087950925</v>
       </c>
       <c r="CX33" s="25">
-        <v>72265.795962277392</v>
+        <v>72257.283862528013</v>
       </c>
       <c r="CY33" s="25">
-        <v>81449.27752719901</v>
+        <v>81447.408979236876</v>
       </c>
       <c r="CZ33" s="25">
-        <v>77741.035183848813</v>
+        <v>78318.531459977836</v>
       </c>
       <c r="DA33" s="25">
-        <v>70736.828222836368</v>
+        <v>71306.100964939513</v>
       </c>
       <c r="DB33" s="20"/>
       <c r="DC33" s="20"/>
@@ -6786,28 +6788,28 @@
         <v>7548.8757146827284</v>
       </c>
       <c r="CT34" s="25">
-        <v>6024.0223060052376</v>
+        <v>5850.6103570475007</v>
       </c>
       <c r="CU34" s="25">
-        <v>3973.8688071625184</v>
+        <v>3858.5416201158532</v>
       </c>
       <c r="CV34" s="25">
-        <v>6463.6515004919311</v>
+        <v>6240.6096838305493</v>
       </c>
       <c r="CW34" s="25">
-        <v>8238.078723152852</v>
+        <v>7981.710427493419</v>
       </c>
       <c r="CX34" s="25">
-        <v>6326.2248521663487</v>
+        <v>6141.5555504368695</v>
       </c>
       <c r="CY34" s="25">
-        <v>4098.3185555509754</v>
+        <v>3981.0290372868094</v>
       </c>
       <c r="CZ34" s="25">
-        <v>6568.605971073488</v>
+        <v>6344.5721556163535</v>
       </c>
       <c r="DA34" s="25">
-        <v>8812.8547690822743</v>
+        <v>8538.5994927040629</v>
       </c>
       <c r="DB34" s="20"/>
       <c r="DC34" s="20"/>
@@ -7357,28 +7359,28 @@
         <v>103446.80219000012</v>
       </c>
       <c r="CT36" s="17">
-        <v>107712.56460649177</v>
+        <v>107241.97172356206</v>
       </c>
       <c r="CU36" s="17">
-        <v>100253.95734219273</v>
+        <v>100132.15730210395</v>
       </c>
       <c r="CV36" s="17">
-        <v>109231.5704944296</v>
+        <v>109395.36839214279</v>
       </c>
       <c r="CW36" s="17">
-        <v>115982.68386395076</v>
+        <v>115986.26843447743</v>
       </c>
       <c r="CX36" s="17">
-        <v>120007.39013474557</v>
+        <v>119508.8076672149</v>
       </c>
       <c r="CY36" s="17">
-        <v>110829.59188150735</v>
+        <v>110547.68704123546</v>
       </c>
       <c r="CZ36" s="17">
-        <v>123408.01783621746</v>
+        <v>123874.60864135824</v>
       </c>
       <c r="DA36" s="17">
-        <v>129274.82673658716</v>
+        <v>129203.7868681507</v>
       </c>
       <c r="DB36" s="20"/>
       <c r="DC36" s="20"/>
@@ -8251,7 +8253,7 @@
     </row>
     <row r="43" spans="1:179" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A43" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B43" s="4"/>
       <c r="C43" s="4"/>
@@ -8576,7 +8578,7 @@
     </row>
     <row r="46" spans="1:179" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B46" s="4"/>
       <c r="C46" s="4"/>
@@ -9753,28 +9755,28 @@
         <v>7.7018938804988011</v>
       </c>
       <c r="CP52" s="14">
-        <v>10.652589258120116</v>
+        <v>9.8366260233250955</v>
       </c>
       <c r="CQ52" s="14">
-        <v>14.927768686684502</v>
+        <v>14.187948792447429</v>
       </c>
       <c r="CR52" s="14">
-        <v>20.218922503175833</v>
+        <v>20.566767320045813</v>
       </c>
       <c r="CS52" s="14">
-        <v>16.95936166662861</v>
+        <v>17.504732254590351</v>
       </c>
       <c r="CT52" s="14">
-        <v>12.25973476090023</v>
+        <v>12.259734760900187</v>
       </c>
       <c r="CU52" s="14">
-        <v>13.687378351807638</v>
+        <v>13.687378351893571</v>
       </c>
       <c r="CV52" s="14">
-        <v>22.290696133670579</v>
+        <v>22.290696133670608</v>
       </c>
       <c r="CW52" s="14">
-        <v>15.950164196554795</v>
+        <v>14.562390065202607</v>
       </c>
       <c r="CX52" s="16"/>
       <c r="CY52" s="16"/>
@@ -10132,28 +10134,28 @@
         <v>13.540864276531337</v>
       </c>
       <c r="CP53" s="14">
-        <v>14.916834819276616</v>
+        <v>14.895064054198116</v>
       </c>
       <c r="CQ53" s="14">
-        <v>13.366090491664224</v>
+        <v>13.589766159351385</v>
       </c>
       <c r="CR53" s="14">
-        <v>15.298394128236325</v>
+        <v>15.781279910056156</v>
       </c>
       <c r="CS53" s="14">
-        <v>15.190067580040449</v>
+        <v>15.283808148404759</v>
       </c>
       <c r="CT53" s="14">
-        <v>17.64594727668829</v>
+        <v>17.654379278881564</v>
       </c>
       <c r="CU53" s="14">
-        <v>14.611575278954419</v>
+        <v>14.383263340530902</v>
       </c>
       <c r="CV53" s="14">
-        <v>16.228401003053406</v>
+        <v>16.603447660776993</v>
       </c>
       <c r="CW53" s="14">
-        <v>15.881685458532573</v>
+        <v>16.719287968455077</v>
       </c>
       <c r="CX53" s="16"/>
       <c r="CY53" s="16"/>
@@ -10511,28 +10513,28 @@
         <v>6.3515261020214382</v>
       </c>
       <c r="CP54" s="14">
-        <v>10.7141045866247</v>
+        <v>7.5244253259932918</v>
       </c>
       <c r="CQ54" s="14">
-        <v>10.613264456312493</v>
+        <v>7.4031140040681009</v>
       </c>
       <c r="CR54" s="14">
-        <v>14.70655510436525</v>
+        <v>10.748365460090724</v>
       </c>
       <c r="CS54" s="14">
-        <v>12.966541583773889</v>
+        <v>9.4510326033876595</v>
       </c>
       <c r="CT54" s="14">
-        <v>8.5708648987550191</v>
+        <v>8.5257553341911319</v>
       </c>
       <c r="CU54" s="14">
-        <v>10.248338870354772</v>
+        <v>10.294034657351588</v>
       </c>
       <c r="CV54" s="14">
-        <v>5.0383328488163244</v>
+        <v>5.0818868001071564</v>
       </c>
       <c r="CW54" s="14">
-        <v>11.302152411152932</v>
+        <v>11.302152411152917</v>
       </c>
       <c r="CX54" s="16"/>
       <c r="CY54" s="16"/>
@@ -11066,28 +11068,28 @@
         <v>10.651845751791257</v>
       </c>
       <c r="CP56" s="14">
-        <v>13.045746007781901</v>
+        <v>12.537052071997778</v>
       </c>
       <c r="CQ56" s="14">
-        <v>13.602941348078446</v>
+        <v>13.465332816545626</v>
       </c>
       <c r="CR56" s="14">
-        <v>16.658246283539825</v>
+        <v>16.825075121793049</v>
       </c>
       <c r="CS56" s="14">
-        <v>15.701860352141566</v>
+        <v>15.692581649020426</v>
       </c>
       <c r="CT56" s="14">
-        <v>15.118306013477607</v>
+        <v>15.139034659400338</v>
       </c>
       <c r="CU56" s="14">
-        <v>14.222574759376982</v>
+        <v>14.063025507696253</v>
       </c>
       <c r="CV56" s="14">
-        <v>17.313862910221076</v>
+        <v>17.586661223990035</v>
       </c>
       <c r="CW56" s="14">
-        <v>15.564911846916374</v>
+        <v>15.480420794292101</v>
       </c>
       <c r="CX56" s="16"/>
       <c r="CY56" s="16"/>
@@ -11952,7 +11954,7 @@
     </row>
     <row r="63" spans="1:175" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A63" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B63" s="4"/>
       <c r="C63" s="4"/>
@@ -12277,7 +12279,7 @@
     </row>
     <row r="66" spans="1:175" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A66" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B66" s="4"/>
       <c r="C66" s="4"/>
@@ -13454,16 +13456,16 @@
         <v>3.2944942293491692</v>
       </c>
       <c r="CP72" s="14">
-        <v>6.8044964182789585</v>
+        <v>6.0169094040716402</v>
       </c>
       <c r="CQ72" s="14">
-        <v>9.7611298728132851</v>
+        <v>9.0545689689752322</v>
       </c>
       <c r="CR72" s="14">
-        <v>14.79892692688523</v>
+        <v>15.131089375876556</v>
       </c>
       <c r="CS72" s="14">
-        <v>12.831612973943379</v>
+        <v>13.357736254982328</v>
       </c>
       <c r="CT72" s="14">
         <v>7.0664300809604867</v>
@@ -13472,10 +13474,10 @@
         <v>8.2428100447218924</v>
       </c>
       <c r="CV72" s="14">
-        <v>16.192261852760367</v>
+        <v>16.192261852760353</v>
       </c>
       <c r="CW72" s="14">
-        <v>11.102553263805831</v>
+        <v>9.7727987920026322</v>
       </c>
       <c r="CX72" s="16"/>
       <c r="CY72" s="16"/>
@@ -13833,28 +13835,28 @@
         <v>8.7292576622182168</v>
       </c>
       <c r="CP73" s="14">
-        <v>10.871754704740511</v>
+        <v>10.850750284320767</v>
       </c>
       <c r="CQ73" s="14">
-        <v>9.7370317520750689</v>
+        <v>9.9535471509640132</v>
       </c>
       <c r="CR73" s="14">
-        <v>12.092634731051803</v>
+        <v>12.562094344670953</v>
       </c>
       <c r="CS73" s="14">
-        <v>12.016107927718124</v>
+        <v>12.107265558264757</v>
       </c>
       <c r="CT73" s="14">
-        <v>14.695587750533235</v>
+        <v>14.703808292387777</v>
       </c>
       <c r="CU73" s="14">
-        <v>11.691637015598673</v>
+        <v>11.469141751441853</v>
       </c>
       <c r="CV73" s="14">
-        <v>12.475501434745297</v>
+        <v>12.838438208587519</v>
       </c>
       <c r="CW73" s="14">
-        <v>12.301128097189221</v>
+        <v>13.112850039177971</v>
       </c>
       <c r="CX73" s="16"/>
       <c r="CY73" s="16"/>
@@ -14212,28 +14214,28 @@
         <v>3.0686870392522962</v>
       </c>
       <c r="CP74" s="14">
-        <v>7.4293755561893278</v>
+        <v>4.3368343197566475</v>
       </c>
       <c r="CQ74" s="14">
-        <v>5.073520547456539</v>
+        <v>2.0241411779144585</v>
       </c>
       <c r="CR74" s="14">
-        <v>9.1544036198075247</v>
+        <v>5.387802577331982</v>
       </c>
       <c r="CS74" s="14">
-        <v>9.129876216263682</v>
+        <v>5.7337639294924116</v>
       </c>
       <c r="CT74" s="14">
-        <v>5.0166239567182629</v>
+        <v>4.9729032636552688</v>
       </c>
       <c r="CU74" s="14">
-        <v>3.1317024901312323</v>
+        <v>3.1744485152729283</v>
       </c>
       <c r="CV74" s="14">
-        <v>1.6237643779768831</v>
+        <v>1.6659024847391208</v>
       </c>
       <c r="CW74" s="14">
-        <v>6.9770642554559856</v>
+        <v>6.977064255455943</v>
       </c>
       <c r="CX74" s="16"/>
       <c r="CY74" s="16"/>
@@ -14767,28 +14769,28 @@
         <v>6.1619997233045751</v>
       </c>
       <c r="CP76" s="14">
-        <v>9.1829224986637712</v>
+        <v>8.7059056673122228</v>
       </c>
       <c r="CQ76" s="14">
-        <v>9.5499076956818669</v>
+        <v>9.4168138657444445</v>
       </c>
       <c r="CR76" s="14">
-        <v>12.731754441161996</v>
+        <v>12.900801029976932</v>
       </c>
       <c r="CS76" s="14">
-        <v>12.118191581143378</v>
+        <v>12.121656715348394</v>
       </c>
       <c r="CT76" s="14">
-        <v>11.414476642693174</v>
+        <v>11.438465506092243</v>
       </c>
       <c r="CU76" s="14">
-        <v>10.548844972989173</v>
+        <v>10.401783023317179</v>
       </c>
       <c r="CV76" s="14">
-        <v>12.97834250447842</v>
+        <v>13.235697691800468</v>
       </c>
       <c r="CW76" s="14">
-        <v>11.460454638408152</v>
+        <v>11.395761422517054</v>
       </c>
       <c r="CX76" s="16"/>
       <c r="CY76" s="16"/>
@@ -15544,7 +15546,7 @@
     </row>
     <row r="82" spans="1:179" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A82" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B82" s="4"/>
       <c r="C82" s="4"/>
@@ -15869,7 +15871,7 @@
     </row>
     <row r="85" spans="1:179" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A85" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B85" s="4"/>
       <c r="C85" s="4"/>
@@ -17068,28 +17070,28 @@
         <v>133.19710686592191</v>
       </c>
       <c r="CT91" s="14">
-        <v>114.38722508909829</v>
+        <v>114.38722508909827</v>
       </c>
       <c r="CU91" s="14">
-        <v>113.55761490605009</v>
+        <v>113.55761491171744</v>
       </c>
       <c r="CV91" s="14">
-        <v>117.48904877407954</v>
+        <v>117.48904877407955</v>
       </c>
       <c r="CW91" s="14">
         <v>138.06989179954004</v>
       </c>
       <c r="CX91" s="14">
-        <v>119.93562817801543</v>
+        <v>119.93562817801539</v>
       </c>
       <c r="CY91" s="14">
-        <v>119.2695156862523</v>
+        <v>119.26951569229489</v>
       </c>
       <c r="CZ91" s="14">
-        <v>123.65554584755361</v>
+        <v>123.65554584755365</v>
       </c>
       <c r="DA91" s="14">
-        <v>144.09413784347828</v>
+        <v>144.09413784347819</v>
       </c>
       <c r="DB91" s="20"/>
       <c r="DC91" s="20"/>
@@ -17459,28 +17461,28 @@
         <v>130.87142444744984</v>
       </c>
       <c r="CT92" s="14">
-        <v>107.10682625358778</v>
+        <v>107.1068262417016</v>
       </c>
       <c r="CU92" s="14">
-        <v>116.51141961649137</v>
+        <v>116.51141961222791</v>
       </c>
       <c r="CV92" s="14">
         <v>126.29735383881275</v>
       </c>
       <c r="CW92" s="14">
-        <v>134.57964667122314</v>
+        <v>134.57964667122312</v>
       </c>
       <c r="CX92" s="14">
-        <v>109.86197709549137</v>
+        <v>109.8619770834123</v>
       </c>
       <c r="CY92" s="14">
-        <v>119.55736075717478</v>
+        <v>119.55736073936517</v>
       </c>
       <c r="CZ92" s="14">
         <v>130.51143849417321</v>
       </c>
       <c r="DA92" s="14">
-        <v>138.87052204122483</v>
+        <v>138.87052204122486</v>
       </c>
       <c r="DB92" s="20"/>
       <c r="DC92" s="20"/>
@@ -17850,10 +17852,10 @@
         <v>139.35955133110886</v>
       </c>
       <c r="CT93" s="14">
-        <v>111.79100692798696</v>
+        <v>111.78832317072995</v>
       </c>
       <c r="CU93" s="14">
-        <v>119.3929720648478</v>
+        <v>119.39297203444687</v>
       </c>
       <c r="CV93" s="14">
         <v>128.55673390107518</v>
@@ -17862,13 +17864,13 @@
         <v>144.25899759424084</v>
       </c>
       <c r="CX93" s="14">
-        <v>115.57452384944813</v>
+        <v>115.5718459951041</v>
       </c>
       <c r="CY93" s="14">
-        <v>127.6317225947444</v>
+        <v>127.6317226300675</v>
       </c>
       <c r="CZ93" s="14">
-        <v>132.87625279490427</v>
+        <v>132.87625279490422</v>
       </c>
       <c r="DA93" s="14">
         <v>150.09139621342192</v>
@@ -18421,28 +18423,28 @@
         <v>132.38260629063194</v>
       </c>
       <c r="CT95" s="14">
-        <v>109.98334805074244</v>
+        <v>109.96888526131508</v>
       </c>
       <c r="CU95" s="14">
-        <v>115.93747371028817</v>
+        <v>115.93789202136055</v>
       </c>
       <c r="CV95" s="14">
-        <v>123.71757587470174</v>
+        <v>123.70899253523848</v>
       </c>
       <c r="CW95" s="14">
-        <v>136.61399287738166</v>
+        <v>136.59881539274909</v>
       </c>
       <c r="CX95" s="14">
-        <v>113.63960141280731</v>
+        <v>113.62065364105334</v>
       </c>
       <c r="CY95" s="14">
-        <v>119.79027697234039</v>
+        <v>119.78272789442165</v>
       </c>
       <c r="CZ95" s="14">
-        <v>128.46521212837155</v>
+        <v>128.46238149381344</v>
       </c>
       <c r="DA95" s="14">
-        <v>141.6447124242176</v>
+        <v>141.60762025518059</v>
       </c>
       <c r="DB95" s="20"/>
       <c r="DC95" s="20"/>
@@ -19167,7 +19169,7 @@
     </row>
     <row r="102" spans="1:179" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A102" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B102" s="4"/>
       <c r="C102" s="4"/>
@@ -19492,7 +19494,7 @@
     </row>
     <row r="105" spans="1:179" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A105" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B105" s="4"/>
       <c r="C105" s="4"/>
@@ -20691,28 +20693,28 @@
         <v>38.580513674291701</v>
       </c>
       <c r="CT111" s="14">
-        <v>37.350157573312266</v>
+        <v>37.242320298284454</v>
       </c>
       <c r="CU111" s="14">
-        <v>22.819346420154822</v>
+        <v>22.699949066778853</v>
       </c>
       <c r="CV111" s="14">
-        <v>29.25494785673644</v>
+        <v>29.297697344628837</v>
       </c>
       <c r="CW111" s="14">
-        <v>38.999824535079512</v>
+        <v>39.184819501178382</v>
       </c>
       <c r="CX111" s="14">
-        <v>36.42269355463737</v>
+        <v>36.310995753381242</v>
       </c>
       <c r="CY111" s="14">
-        <v>22.712425067235973</v>
+        <v>22.625190649089625</v>
       </c>
       <c r="CZ111" s="14">
-        <v>30.496037296908675</v>
+        <v>30.469746875143716</v>
       </c>
       <c r="DA111" s="14">
-        <v>39.129836091333956</v>
+        <v>38.873313289402567</v>
       </c>
       <c r="DB111" s="20"/>
       <c r="DC111" s="20"/>
@@ -21082,28 +21084,28 @@
         <v>53.737544437002192</v>
       </c>
       <c r="CT112" s="14">
-        <v>56.965239468319396</v>
+        <v>57.211895011623128</v>
       </c>
       <c r="CU112" s="14">
-        <v>73.098710625381941</v>
+        <v>73.331764798525441</v>
       </c>
       <c r="CV112" s="14">
-        <v>64.596212272656402</v>
+        <v>64.774119053582552</v>
       </c>
       <c r="CW112" s="14">
-        <v>53.499843100570644</v>
+        <v>53.547675010277452</v>
       </c>
       <c r="CX112" s="14">
-        <v>58.216019599082827</v>
+        <v>58.461754650567563</v>
       </c>
       <c r="CY112" s="14">
-        <v>73.347658230298194</v>
+        <v>73.537647514089883</v>
       </c>
       <c r="CZ112" s="14">
-        <v>63.998527344124589</v>
+        <v>64.23250326369849</v>
       </c>
       <c r="DA112" s="14">
-        <v>53.646490887074535</v>
+        <v>54.122131323881895</v>
       </c>
       <c r="DB112" s="20"/>
       <c r="DC112" s="20"/>
@@ -21473,28 +21475,28 @@
         <v>7.6819418887061088</v>
       </c>
       <c r="CT113" s="14">
-        <v>5.6846029583683366</v>
+        <v>5.5457846900924261</v>
       </c>
       <c r="CU113" s="14">
-        <v>4.0819429544632531</v>
+        <v>3.9682861346956968</v>
       </c>
       <c r="CV113" s="14">
-        <v>6.1488398706071692</v>
+        <v>5.9281836017886143</v>
       </c>
       <c r="CW113" s="14">
-        <v>7.500332364349843</v>
+        <v>7.267505488544181</v>
       </c>
       <c r="CX113" s="14">
-        <v>5.3612868462798131</v>
+        <v>5.227249596051184</v>
       </c>
       <c r="CY113" s="14">
-        <v>3.9399167024658341</v>
+        <v>3.8371618368204978</v>
       </c>
       <c r="CZ113" s="14">
-        <v>5.5054353589667455</v>
+        <v>5.2977498611577998</v>
       </c>
       <c r="DA113" s="14">
-        <v>7.2236730215914964</v>
+        <v>7.0045553867155288</v>
       </c>
       <c r="DB113" s="20"/>
       <c r="DC113" s="20"/>
@@ -22938,7 +22940,7 @@
     </row>
     <row r="122" spans="1:179" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A122" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B122" s="4"/>
       <c r="C122" s="4"/>
@@ -23263,7 +23265,7 @@
     </row>
     <row r="125" spans="1:179" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A125" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B125" s="4"/>
       <c r="C125" s="4"/>
@@ -24462,28 +24464,28 @@
         <v>38.344593755893442</v>
       </c>
       <c r="CT131" s="14">
-        <v>35.912186670635307</v>
+        <v>35.80379229024161</v>
       </c>
       <c r="CU131" s="14">
-        <v>23.297577867071826</v>
+        <v>23.175761888276767</v>
       </c>
       <c r="CV131" s="14">
-        <v>30.805860366917319</v>
+        <v>30.848735775159142</v>
       </c>
       <c r="CW131" s="14">
-        <v>38.588584968183739</v>
+        <v>38.767321792436519</v>
       </c>
       <c r="CX131" s="14">
-        <v>34.510682445306259</v>
+        <v>34.39911171126829</v>
       </c>
       <c r="CY131" s="14">
-        <v>22.811593338525903</v>
+        <v>22.722545986278334</v>
       </c>
       <c r="CZ131" s="14">
-        <v>31.682201340584758</v>
+        <v>31.654190843330294</v>
       </c>
       <c r="DA131" s="14">
-        <v>38.464676379717318</v>
+        <v>38.202507532443192</v>
       </c>
       <c r="DB131" s="20"/>
       <c r="DC131" s="20"/>
@@ -24853,28 +24855,28 @@
         <v>54.358055765531347</v>
       </c>
       <c r="CT132" s="14">
-        <v>58.495130314144603</v>
+        <v>58.740684780612121</v>
       </c>
       <c r="CU132" s="14">
-        <v>72.738619693091636</v>
+        <v>72.97078910585148</v>
       </c>
       <c r="CV132" s="14">
-        <v>63.276755610098633</v>
+        <v>63.446626290389894</v>
       </c>
       <c r="CW132" s="14">
-        <v>54.308562736368252</v>
+        <v>54.351078743052369</v>
       </c>
       <c r="CX132" s="14">
-        <v>60.217788155493245</v>
+        <v>60.461890025491826</v>
       </c>
       <c r="CY132" s="14">
-        <v>73.49055080368781</v>
+        <v>73.676266920768882</v>
       </c>
       <c r="CZ132" s="14">
-        <v>62.995125071228216</v>
+        <v>63.22403946940058</v>
       </c>
       <c r="DA132" s="14">
-        <v>54.718176777734982</v>
+        <v>55.188863030543864</v>
       </c>
       <c r="DB132" s="20"/>
       <c r="DC132" s="20"/>
@@ -25244,28 +25246,28 @@
         <v>7.2973504785752139</v>
       </c>
       <c r="CT133" s="14">
-        <v>5.5926830152200955</v>
+        <v>5.4555229291462819</v>
       </c>
       <c r="CU133" s="14">
-        <v>3.963802439836539</v>
+        <v>3.8534490058717417</v>
       </c>
       <c r="CV133" s="14">
-        <v>5.9173840229840442</v>
+        <v>5.7046379344509566</v>
       </c>
       <c r="CW133" s="14">
-        <v>7.1028522954480238</v>
+        <v>6.8815994645111109</v>
       </c>
       <c r="CX133" s="14">
-        <v>5.2715293992004959</v>
+        <v>5.1389982632398858</v>
       </c>
       <c r="CY133" s="14">
-        <v>3.6978558577863057</v>
+        <v>3.6011870929527845</v>
       </c>
       <c r="CZ133" s="14">
-        <v>5.3226735881870315</v>
+        <v>5.121769687269131</v>
       </c>
       <c r="DA133" s="14">
-        <v>6.81714684254771</v>
+        <v>6.6086294370129375</v>
       </c>
       <c r="DB133" s="20"/>
       <c r="DC133" s="20"/>

--- a/Data/National Accounts/PSA-20HHSW_2018PSNA_Qrt.xlsx
+++ b/Data/National Accounts/PSA-20HHSW_2018PSNA_Qrt.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\Shared drives\QNAP\NAP Dissemination\As of April 2026\Tables\NAP Q1 2000 to Q4 2025\Qtr\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Shared drives\QNAP\NAP Dissemination\As of May 2026\Tables\NAP Q1 2000 to Q1 2026\Qtr\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26062675-90B5-47FA-9744-0B240E5225FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5490CE1-7F2D-4964-B94B-8C726F4E5616}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="794" xr2:uid="{736930C2-BFBB-46C3-AE9E-AECFC8C3145D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="794" xr2:uid="{736930C2-BFBB-46C3-AE9E-AECFC8C3145D}"/>
   </bookViews>
   <sheets>
     <sheet name="HHSW" sheetId="20" r:id="rId1"/>
@@ -356,7 +356,7 @@
     <definedName name="pet">#REF!</definedName>
     <definedName name="plastic">#REF!</definedName>
     <definedName name="ply">#REF!</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">HHSW!$A$1:$DA$138</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">HHSW!$A$1:$DB$138</definedName>
     <definedName name="_xlnm.Print_Area">#REF!</definedName>
     <definedName name="PRINT_AREA_MI">#REF!</definedName>
     <definedName name="Print_Titles_MI">#REF!,#REF!</definedName>
@@ -530,7 +530,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="853" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="862" uniqueCount="55">
   <si>
     <t>National Accounts of the Philippines</t>
   </si>
@@ -689,10 +689,13 @@
     <t>Table 21.7 Gross Value Added in Human Health and Social Work Activities, by Industry</t>
   </si>
   <si>
-    <t>Q1 2000 to Q4 2025</t>
+    <t>Q1 2000 to Q1 2026</t>
   </si>
   <si>
-    <t>As of April 2026</t>
+    <t>As of May 2026</t>
+  </si>
+  <si>
+    <t>2025 - 2026</t>
   </si>
 </sst>
 </file>
@@ -1215,8 +1218,8 @@
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="49.28515625" style="4" customWidth="1"/>
-    <col min="2" max="105" width="13" style="21" customWidth="1"/>
-    <col min="106" max="16384" width="10" style="21"/>
+    <col min="2" max="106" width="13" style="21" customWidth="1"/>
+    <col min="107" max="16384" width="10" style="21"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:179" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.2">
@@ -1358,6 +1361,7 @@
       <c r="CY8" s="4"/>
       <c r="CZ8" s="4"/>
       <c r="DA8" s="4"/>
+      <c r="DB8" s="4"/>
     </row>
     <row r="9" spans="1:179" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A9" s="15"/>
@@ -1517,6 +1521,9 @@
       <c r="CY9" s="24"/>
       <c r="CZ9" s="24"/>
       <c r="DA9" s="24"/>
+      <c r="DB9" s="24">
+        <v>2026</v>
+      </c>
     </row>
     <row r="10" spans="1:179" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
@@ -1833,6 +1840,9 @@
       </c>
       <c r="DA10" s="12" t="s">
         <v>5</v>
+      </c>
+      <c r="DB10" s="12" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:179" s="18" customFormat="1" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -1941,6 +1951,7 @@
       <c r="CY11" s="4"/>
       <c r="CZ11" s="4"/>
       <c r="DA11" s="4"/>
+      <c r="DB11" s="4"/>
     </row>
     <row r="12" spans="1:179" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
@@ -2258,7 +2269,9 @@
       <c r="DA12" s="25">
         <v>71123.550010637642</v>
       </c>
-      <c r="DB12" s="20"/>
+      <c r="DB12" s="25">
+        <v>53351.656396032027</v>
+      </c>
       <c r="DC12" s="20"/>
       <c r="DD12" s="20"/>
       <c r="DE12" s="20"/>
@@ -2649,7 +2662,9 @@
       <c r="DA13" s="25">
         <v>99023.154657254374</v>
       </c>
-      <c r="DB13" s="20"/>
+      <c r="DB13" s="25">
+        <v>89459.018989939999</v>
+      </c>
       <c r="DC13" s="20"/>
       <c r="DD13" s="20"/>
       <c r="DE13" s="20"/>
@@ -3040,7 +3055,9 @@
       <c r="DA14" s="25">
         <v>12815.703195671689</v>
       </c>
-      <c r="DB14" s="20"/>
+      <c r="DB14" s="25">
+        <v>7406.1010721528382</v>
+      </c>
       <c r="DC14" s="20"/>
       <c r="DD14" s="20"/>
       <c r="DE14" s="20"/>
@@ -3220,7 +3237,7 @@
       <c r="CY15" s="8"/>
       <c r="CZ15" s="8"/>
       <c r="DA15" s="8"/>
-      <c r="DB15" s="20"/>
+      <c r="DB15" s="8"/>
       <c r="DC15" s="20"/>
       <c r="DD15" s="20"/>
       <c r="DE15" s="20"/>
@@ -3611,7 +3628,9 @@
       <c r="DA16" s="17">
         <v>182962.40786356371</v>
       </c>
-      <c r="DB16" s="20"/>
+      <c r="DB16" s="17">
+        <v>150216.77645812486</v>
+      </c>
       <c r="DC16" s="20"/>
       <c r="DD16" s="20"/>
       <c r="DE16" s="20"/>
@@ -3792,6 +3811,7 @@
       <c r="CY17" s="10"/>
       <c r="CZ17" s="10"/>
       <c r="DA17" s="10"/>
+      <c r="DB17" s="10"/>
     </row>
     <row r="18" spans="1:179" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A18" s="11" t="s">
@@ -3901,6 +3921,7 @@
       <c r="CY18" s="4"/>
       <c r="CZ18" s="4"/>
       <c r="DA18" s="4"/>
+      <c r="DB18" s="4"/>
     </row>
     <row r="19" spans="1:179" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="8"/>
@@ -4007,7 +4028,7 @@
       <c r="CY19" s="8"/>
       <c r="CZ19" s="8"/>
       <c r="DA19" s="8"/>
-      <c r="DB19" s="20"/>
+      <c r="DB19" s="8"/>
       <c r="DC19" s="20"/>
       <c r="DD19" s="20"/>
       <c r="DE19" s="20"/>
@@ -4187,7 +4208,7 @@
       <c r="CY20" s="8"/>
       <c r="CZ20" s="8"/>
       <c r="DA20" s="8"/>
-      <c r="DB20" s="20"/>
+      <c r="DB20" s="8"/>
       <c r="DC20" s="20"/>
       <c r="DD20" s="20"/>
       <c r="DE20" s="20"/>
@@ -4370,6 +4391,7 @@
       <c r="CY21" s="4"/>
       <c r="CZ21" s="4"/>
       <c r="DA21" s="4"/>
+      <c r="DB21" s="4"/>
     </row>
     <row r="22" spans="1:179" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
@@ -4479,6 +4501,7 @@
       <c r="CY22" s="4"/>
       <c r="CZ22" s="4"/>
       <c r="DA22" s="4"/>
+      <c r="DB22" s="4"/>
     </row>
     <row r="23" spans="1:179" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A23" s="4" t="s">
@@ -4588,6 +4611,7 @@
       <c r="CY23" s="4"/>
       <c r="CZ23" s="4"/>
       <c r="DA23" s="4"/>
+      <c r="DB23" s="4"/>
     </row>
     <row r="24" spans="1:179" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A24" s="4"/>
@@ -4695,6 +4719,7 @@
       <c r="CY24" s="4"/>
       <c r="CZ24" s="4"/>
       <c r="DA24" s="4"/>
+      <c r="DB24" s="4"/>
     </row>
     <row r="25" spans="1:179" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A25" s="4" t="s">
@@ -4804,6 +4829,7 @@
       <c r="CY25" s="4"/>
       <c r="CZ25" s="4"/>
       <c r="DA25" s="4"/>
+      <c r="DB25" s="4"/>
     </row>
     <row r="26" spans="1:179" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A26" s="4" t="s">
@@ -4913,6 +4939,7 @@
       <c r="CY26" s="4"/>
       <c r="CZ26" s="4"/>
       <c r="DA26" s="4"/>
+      <c r="DB26" s="4"/>
     </row>
     <row r="27" spans="1:179" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A27" s="4" t="s">
@@ -5022,6 +5049,7 @@
       <c r="CY27" s="4"/>
       <c r="CZ27" s="4"/>
       <c r="DA27" s="4"/>
+      <c r="DB27" s="4"/>
     </row>
     <row r="28" spans="1:179" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A28" s="4"/>
@@ -5129,6 +5157,7 @@
       <c r="CY28" s="4"/>
       <c r="CZ28" s="4"/>
       <c r="DA28" s="4"/>
+      <c r="DB28" s="4"/>
     </row>
     <row r="29" spans="1:179" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A29" s="15"/>
@@ -5288,6 +5317,9 @@
       <c r="CY29" s="24"/>
       <c r="CZ29" s="24"/>
       <c r="DA29" s="24"/>
+      <c r="DB29" s="24">
+        <v>2026</v>
+      </c>
     </row>
     <row r="30" spans="1:179" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A30" s="5" t="s">
@@ -5604,6 +5636,9 @@
       </c>
       <c r="DA30" s="12" t="s">
         <v>5</v>
+      </c>
+      <c r="DB30" s="12" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="31" spans="1:179" s="18" customFormat="1" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -5712,6 +5747,7 @@
       <c r="CY31" s="4"/>
       <c r="CZ31" s="4"/>
       <c r="DA31" s="4"/>
+      <c r="DB31" s="4"/>
     </row>
     <row r="32" spans="1:179" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="4" t="s">
@@ -6029,7 +6065,9 @@
       <c r="DA32" s="25">
         <v>49359.086410507116</v>
       </c>
-      <c r="DB32" s="20"/>
+      <c r="DB32" s="25">
+        <v>43549.587113124842</v>
+      </c>
       <c r="DC32" s="20"/>
       <c r="DD32" s="20"/>
       <c r="DE32" s="20"/>
@@ -6420,7 +6458,9 @@
       <c r="DA33" s="25">
         <v>71306.100964939513</v>
       </c>
-      <c r="DB33" s="20"/>
+      <c r="DB33" s="25">
+        <v>78589.860482718126</v>
+      </c>
       <c r="DC33" s="20"/>
       <c r="DD33" s="20"/>
       <c r="DE33" s="20"/>
@@ -6811,7 +6851,9 @@
       <c r="DA34" s="25">
         <v>8538.5994927040629</v>
       </c>
-      <c r="DB34" s="20"/>
+      <c r="DB34" s="25">
+        <v>6163.6601380942939</v>
+      </c>
       <c r="DC34" s="20"/>
       <c r="DD34" s="20"/>
       <c r="DE34" s="20"/>
@@ -6991,7 +7033,7 @@
       <c r="CY35" s="8"/>
       <c r="CZ35" s="8"/>
       <c r="DA35" s="8"/>
-      <c r="DB35" s="20"/>
+      <c r="DB35" s="8"/>
       <c r="DC35" s="20"/>
       <c r="DD35" s="20"/>
       <c r="DE35" s="20"/>
@@ -7382,7 +7424,9 @@
       <c r="DA36" s="17">
         <v>129203.7868681507</v>
       </c>
-      <c r="DB36" s="20"/>
+      <c r="DB36" s="17">
+        <v>128303.10773393726</v>
+      </c>
       <c r="DC36" s="20"/>
       <c r="DD36" s="20"/>
       <c r="DE36" s="20"/>
@@ -7563,6 +7607,7 @@
       <c r="CY37" s="10"/>
       <c r="CZ37" s="10"/>
       <c r="DA37" s="10"/>
+      <c r="DB37" s="10"/>
     </row>
     <row r="38" spans="1:179" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A38" s="11" t="s">
@@ -7672,6 +7717,7 @@
       <c r="CY38" s="4"/>
       <c r="CZ38" s="4"/>
       <c r="DA38" s="4"/>
+      <c r="DB38" s="4"/>
     </row>
     <row r="39" spans="1:179" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B39" s="8"/>
@@ -7778,7 +7824,7 @@
       <c r="CY39" s="7"/>
       <c r="CZ39" s="7"/>
       <c r="DA39" s="7"/>
-      <c r="DB39" s="20"/>
+      <c r="DB39" s="7"/>
       <c r="DC39" s="20"/>
       <c r="DD39" s="20"/>
       <c r="DE39" s="20"/>
@@ -7958,7 +8004,7 @@
       <c r="CY40" s="7"/>
       <c r="CZ40" s="7"/>
       <c r="DA40" s="7"/>
-      <c r="DB40" s="20"/>
+      <c r="DB40" s="7"/>
       <c r="DC40" s="20"/>
       <c r="DD40" s="20"/>
       <c r="DE40" s="20"/>
@@ -8141,6 +8187,7 @@
       <c r="CY41" s="26"/>
       <c r="CZ41" s="26"/>
       <c r="DA41" s="26"/>
+      <c r="DB41" s="26"/>
     </row>
     <row r="42" spans="1:179" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A42" s="4" t="s">
@@ -8250,6 +8297,7 @@
       <c r="CY42" s="26"/>
       <c r="CZ42" s="26"/>
       <c r="DA42" s="26"/>
+      <c r="DB42" s="26"/>
     </row>
     <row r="43" spans="1:179" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A43" s="4" t="s">
@@ -8359,6 +8407,7 @@
       <c r="CY43" s="26"/>
       <c r="CZ43" s="26"/>
       <c r="DA43" s="26"/>
+      <c r="DB43" s="26"/>
     </row>
     <row r="44" spans="1:179" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A44" s="4"/>
@@ -8466,6 +8515,7 @@
       <c r="CY44" s="26"/>
       <c r="CZ44" s="26"/>
       <c r="DA44" s="26"/>
+      <c r="DB44" s="26"/>
     </row>
     <row r="45" spans="1:179" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A45" s="4" t="s">
@@ -8575,6 +8625,7 @@
       <c r="CY45" s="26"/>
       <c r="CZ45" s="26"/>
       <c r="DA45" s="26"/>
+      <c r="DB45" s="26"/>
     </row>
     <row r="46" spans="1:179" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
@@ -8684,6 +8735,7 @@
       <c r="CY46" s="26"/>
       <c r="CZ46" s="26"/>
       <c r="DA46" s="26"/>
+      <c r="DB46" s="26"/>
     </row>
     <row r="47" spans="1:179" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A47" s="4" t="s">
@@ -8793,6 +8845,7 @@
       <c r="CY47" s="26"/>
       <c r="CZ47" s="26"/>
       <c r="DA47" s="26"/>
+      <c r="DB47" s="26"/>
     </row>
     <row r="48" spans="1:179" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A48" s="4"/>
@@ -8896,10 +8949,11 @@
       <c r="CU48" s="4"/>
       <c r="CV48" s="4"/>
       <c r="CW48" s="4"/>
-      <c r="CX48" s="26"/>
+      <c r="CX48" s="4"/>
       <c r="CY48" s="26"/>
       <c r="CZ48" s="26"/>
       <c r="DA48" s="26"/>
+      <c r="DB48" s="26"/>
     </row>
     <row r="49" spans="1:175" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A49" s="15"/>
@@ -9053,10 +9107,13 @@
       <c r="CU49" s="24"/>
       <c r="CV49" s="24"/>
       <c r="CW49" s="24"/>
-      <c r="CX49" s="27"/>
+      <c r="CX49" s="24" t="s">
+        <v>54</v>
+      </c>
       <c r="CY49" s="27"/>
       <c r="CZ49" s="27"/>
       <c r="DA49" s="27"/>
+      <c r="DB49" s="27"/>
     </row>
     <row r="50" spans="1:175" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A50" s="5" t="s">
@@ -9362,10 +9419,13 @@
       <c r="CW50" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="CX50" s="28"/>
+      <c r="CX50" s="5" t="s">
+        <v>2</v>
+      </c>
       <c r="CY50" s="28"/>
       <c r="CZ50" s="28"/>
       <c r="DA50" s="28"/>
+      <c r="DB50" s="28"/>
     </row>
     <row r="51" spans="1:175" s="18" customFormat="1" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="6"/>
@@ -9469,10 +9529,11 @@
       <c r="CU51" s="4"/>
       <c r="CV51" s="4"/>
       <c r="CW51" s="4"/>
-      <c r="CX51" s="26"/>
+      <c r="CX51" s="4"/>
       <c r="CY51" s="26"/>
       <c r="CZ51" s="26"/>
       <c r="DA51" s="26"/>
+      <c r="DB51" s="26"/>
     </row>
     <row r="52" spans="1:175" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="4" t="s">
@@ -9778,11 +9839,13 @@
       <c r="CW52" s="14">
         <v>14.562390065202607</v>
       </c>
-      <c r="CX52" s="16"/>
+      <c r="CX52" s="14">
+        <v>8.2063011949943956</v>
+      </c>
       <c r="CY52" s="16"/>
       <c r="CZ52" s="16"/>
       <c r="DA52" s="16"/>
-      <c r="DB52" s="20"/>
+      <c r="DB52" s="16"/>
       <c r="DC52" s="20"/>
       <c r="DD52" s="20"/>
       <c r="DE52" s="20"/>
@@ -10157,11 +10220,13 @@
       <c r="CW53" s="14">
         <v>16.719287968455077</v>
       </c>
-      <c r="CX53" s="16"/>
+      <c r="CX53" s="14">
+        <v>12.692519471098223</v>
+      </c>
       <c r="CY53" s="16"/>
       <c r="CZ53" s="16"/>
       <c r="DA53" s="16"/>
-      <c r="DB53" s="20"/>
+      <c r="DB53" s="16"/>
       <c r="DC53" s="20"/>
       <c r="DD53" s="20"/>
       <c r="DE53" s="20"/>
@@ -10536,11 +10601,13 @@
       <c r="CW54" s="14">
         <v>11.302152411152917</v>
       </c>
-      <c r="CX54" s="16"/>
+      <c r="CX54" s="14">
+        <v>4.3420103636321272</v>
+      </c>
       <c r="CY54" s="16"/>
       <c r="CZ54" s="16"/>
       <c r="DA54" s="16"/>
-      <c r="DB54" s="20"/>
+      <c r="DB54" s="16"/>
       <c r="DC54" s="20"/>
       <c r="DD54" s="20"/>
       <c r="DE54" s="20"/>
@@ -10712,11 +10779,11 @@
       <c r="CU55" s="8"/>
       <c r="CV55" s="8"/>
       <c r="CW55" s="8"/>
-      <c r="CX55" s="7"/>
+      <c r="CX55" s="8"/>
       <c r="CY55" s="7"/>
       <c r="CZ55" s="7"/>
       <c r="DA55" s="7"/>
-      <c r="DB55" s="20"/>
+      <c r="DB55" s="7"/>
       <c r="DC55" s="20"/>
       <c r="DD55" s="20"/>
       <c r="DE55" s="20"/>
@@ -11091,11 +11158,13 @@
       <c r="CW56" s="14">
         <v>15.480420794292101</v>
       </c>
-      <c r="CX56" s="16"/>
+      <c r="CX56" s="14">
+        <v>10.627026989786501</v>
+      </c>
       <c r="CY56" s="16"/>
       <c r="CZ56" s="16"/>
       <c r="DA56" s="16"/>
-      <c r="DB56" s="20"/>
+      <c r="DB56" s="16"/>
       <c r="DC56" s="20"/>
       <c r="DD56" s="20"/>
       <c r="DE56" s="20"/>
@@ -11268,10 +11337,11 @@
       <c r="CU57" s="10"/>
       <c r="CV57" s="10"/>
       <c r="CW57" s="10"/>
-      <c r="CX57" s="29"/>
+      <c r="CX57" s="10"/>
       <c r="CY57" s="29"/>
       <c r="CZ57" s="29"/>
       <c r="DA57" s="29"/>
+      <c r="DB57" s="29"/>
     </row>
     <row r="58" spans="1:175" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A58" s="11" t="s">
@@ -11377,10 +11447,11 @@
       <c r="CU58" s="4"/>
       <c r="CV58" s="4"/>
       <c r="CW58" s="4"/>
-      <c r="CX58" s="26"/>
+      <c r="CX58" s="4"/>
       <c r="CY58" s="26"/>
       <c r="CZ58" s="26"/>
       <c r="DA58" s="26"/>
+      <c r="DB58" s="26"/>
     </row>
     <row r="59" spans="1:175" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B59" s="8"/>
@@ -11483,11 +11554,11 @@
       <c r="CU59" s="8"/>
       <c r="CV59" s="8"/>
       <c r="CW59" s="8"/>
-      <c r="CX59" s="7"/>
+      <c r="CX59" s="8"/>
       <c r="CY59" s="7"/>
       <c r="CZ59" s="7"/>
       <c r="DA59" s="7"/>
-      <c r="DB59" s="20"/>
+      <c r="DB59" s="7"/>
       <c r="DC59" s="20"/>
       <c r="DD59" s="20"/>
       <c r="DE59" s="20"/>
@@ -11659,11 +11730,11 @@
       <c r="CU60" s="8"/>
       <c r="CV60" s="8"/>
       <c r="CW60" s="8"/>
-      <c r="CX60" s="7"/>
+      <c r="CX60" s="8"/>
       <c r="CY60" s="7"/>
       <c r="CZ60" s="7"/>
       <c r="DA60" s="7"/>
-      <c r="DB60" s="20"/>
+      <c r="DB60" s="7"/>
       <c r="DC60" s="20"/>
       <c r="DD60" s="20"/>
       <c r="DE60" s="20"/>
@@ -11838,10 +11909,11 @@
       <c r="CU61" s="4"/>
       <c r="CV61" s="4"/>
       <c r="CW61" s="4"/>
-      <c r="CX61" s="26"/>
+      <c r="CX61" s="4"/>
       <c r="CY61" s="26"/>
       <c r="CZ61" s="26"/>
       <c r="DA61" s="26"/>
+      <c r="DB61" s="26"/>
     </row>
     <row r="62" spans="1:175" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A62" s="4" t="s">
@@ -11947,10 +12019,11 @@
       <c r="CU62" s="4"/>
       <c r="CV62" s="4"/>
       <c r="CW62" s="4"/>
-      <c r="CX62" s="26"/>
+      <c r="CX62" s="4"/>
       <c r="CY62" s="26"/>
       <c r="CZ62" s="26"/>
       <c r="DA62" s="26"/>
+      <c r="DB62" s="26"/>
     </row>
     <row r="63" spans="1:175" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A63" s="4" t="s">
@@ -12056,10 +12129,11 @@
       <c r="CU63" s="4"/>
       <c r="CV63" s="4"/>
       <c r="CW63" s="4"/>
-      <c r="CX63" s="26"/>
+      <c r="CX63" s="4"/>
       <c r="CY63" s="26"/>
       <c r="CZ63" s="26"/>
       <c r="DA63" s="26"/>
+      <c r="DB63" s="26"/>
     </row>
     <row r="64" spans="1:175" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A64" s="4"/>
@@ -12163,10 +12237,11 @@
       <c r="CU64" s="4"/>
       <c r="CV64" s="4"/>
       <c r="CW64" s="4"/>
-      <c r="CX64" s="26"/>
+      <c r="CX64" s="4"/>
       <c r="CY64" s="26"/>
       <c r="CZ64" s="26"/>
       <c r="DA64" s="26"/>
+      <c r="DB64" s="26"/>
     </row>
     <row r="65" spans="1:175" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A65" s="4" t="s">
@@ -12272,10 +12347,11 @@
       <c r="CU65" s="4"/>
       <c r="CV65" s="4"/>
       <c r="CW65" s="4"/>
-      <c r="CX65" s="26"/>
+      <c r="CX65" s="4"/>
       <c r="CY65" s="26"/>
       <c r="CZ65" s="26"/>
       <c r="DA65" s="26"/>
+      <c r="DB65" s="26"/>
     </row>
     <row r="66" spans="1:175" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A66" s="4" t="s">
@@ -12381,10 +12457,11 @@
       <c r="CU66" s="4"/>
       <c r="CV66" s="4"/>
       <c r="CW66" s="4"/>
-      <c r="CX66" s="26"/>
+      <c r="CX66" s="4"/>
       <c r="CY66" s="26"/>
       <c r="CZ66" s="26"/>
       <c r="DA66" s="26"/>
+      <c r="DB66" s="26"/>
     </row>
     <row r="67" spans="1:175" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A67" s="4" t="s">
@@ -12490,10 +12567,11 @@
       <c r="CU67" s="4"/>
       <c r="CV67" s="4"/>
       <c r="CW67" s="4"/>
-      <c r="CX67" s="26"/>
+      <c r="CX67" s="4"/>
       <c r="CY67" s="26"/>
       <c r="CZ67" s="26"/>
       <c r="DA67" s="26"/>
+      <c r="DB67" s="26"/>
     </row>
     <row r="68" spans="1:175" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A68" s="4"/>
@@ -12597,10 +12675,11 @@
       <c r="CU68" s="4"/>
       <c r="CV68" s="4"/>
       <c r="CW68" s="4"/>
-      <c r="CX68" s="26"/>
+      <c r="CX68" s="4"/>
       <c r="CY68" s="26"/>
       <c r="CZ68" s="26"/>
       <c r="DA68" s="26"/>
+      <c r="DB68" s="26"/>
     </row>
     <row r="69" spans="1:175" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A69" s="15"/>
@@ -12754,10 +12833,13 @@
       <c r="CU69" s="24"/>
       <c r="CV69" s="24"/>
       <c r="CW69" s="24"/>
-      <c r="CX69" s="27"/>
+      <c r="CX69" s="24" t="s">
+        <v>54</v>
+      </c>
       <c r="CY69" s="27"/>
       <c r="CZ69" s="27"/>
       <c r="DA69" s="27"/>
+      <c r="DB69" s="27"/>
     </row>
     <row r="70" spans="1:175" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A70" s="5" t="s">
@@ -13063,10 +13145,13 @@
       <c r="CW70" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="CX70" s="28"/>
+      <c r="CX70" s="5" t="s">
+        <v>2</v>
+      </c>
       <c r="CY70" s="28"/>
       <c r="CZ70" s="28"/>
       <c r="DA70" s="28"/>
+      <c r="DB70" s="28"/>
     </row>
     <row r="71" spans="1:175" s="18" customFormat="1" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="6"/>
@@ -13170,10 +13255,11 @@
       <c r="CU71" s="4"/>
       <c r="CV71" s="4"/>
       <c r="CW71" s="4"/>
-      <c r="CX71" s="26"/>
+      <c r="CX71" s="4"/>
       <c r="CY71" s="26"/>
       <c r="CZ71" s="26"/>
       <c r="DA71" s="26"/>
+      <c r="DB71" s="26"/>
     </row>
     <row r="72" spans="1:175" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="4" t="s">
@@ -13479,11 +13565,13 @@
       <c r="CW72" s="14">
         <v>9.7727987920026322</v>
       </c>
-      <c r="CX72" s="16"/>
+      <c r="CX72" s="14">
+        <v>5.934373006047295</v>
+      </c>
       <c r="CY72" s="16"/>
       <c r="CZ72" s="16"/>
       <c r="DA72" s="16"/>
-      <c r="DB72" s="20"/>
+      <c r="DB72" s="16"/>
       <c r="DC72" s="20"/>
       <c r="DD72" s="20"/>
       <c r="DE72" s="20"/>
@@ -13858,11 +13946,13 @@
       <c r="CW73" s="14">
         <v>13.112850039177971</v>
       </c>
-      <c r="CX73" s="16"/>
+      <c r="CX73" s="14">
+        <v>8.7639283981917373</v>
+      </c>
       <c r="CY73" s="16"/>
       <c r="CZ73" s="16"/>
       <c r="DA73" s="16"/>
-      <c r="DB73" s="20"/>
+      <c r="DB73" s="16"/>
       <c r="DC73" s="20"/>
       <c r="DD73" s="20"/>
       <c r="DE73" s="20"/>
@@ -14237,11 +14327,13 @@
       <c r="CW74" s="14">
         <v>6.977064255455943</v>
       </c>
-      <c r="CX74" s="16"/>
+      <c r="CX74" s="14">
+        <v>0.35991838673268717</v>
+      </c>
       <c r="CY74" s="16"/>
       <c r="CZ74" s="16"/>
       <c r="DA74" s="16"/>
-      <c r="DB74" s="20"/>
+      <c r="DB74" s="16"/>
       <c r="DC74" s="20"/>
       <c r="DD74" s="20"/>
       <c r="DE74" s="20"/>
@@ -14413,11 +14505,11 @@
       <c r="CU75" s="8"/>
       <c r="CV75" s="8"/>
       <c r="CW75" s="8"/>
-      <c r="CX75" s="7"/>
+      <c r="CX75" s="8"/>
       <c r="CY75" s="7"/>
       <c r="CZ75" s="7"/>
       <c r="DA75" s="7"/>
-      <c r="DB75" s="20"/>
+      <c r="DB75" s="7"/>
       <c r="DC75" s="20"/>
       <c r="DD75" s="20"/>
       <c r="DE75" s="20"/>
@@ -14792,11 +14884,13 @@
       <c r="CW76" s="14">
         <v>11.395761422517054</v>
       </c>
-      <c r="CX76" s="16"/>
+      <c r="CX76" s="14">
+        <v>7.3587045493843704</v>
+      </c>
       <c r="CY76" s="16"/>
       <c r="CZ76" s="16"/>
       <c r="DA76" s="16"/>
-      <c r="DB76" s="20"/>
+      <c r="DB76" s="16"/>
       <c r="DC76" s="20"/>
       <c r="DD76" s="20"/>
       <c r="DE76" s="20"/>
@@ -14969,10 +15063,11 @@
       <c r="CU77" s="10"/>
       <c r="CV77" s="10"/>
       <c r="CW77" s="10"/>
-      <c r="CX77" s="29"/>
+      <c r="CX77" s="10"/>
       <c r="CY77" s="29"/>
       <c r="CZ77" s="29"/>
       <c r="DA77" s="29"/>
+      <c r="DB77" s="29"/>
     </row>
     <row r="78" spans="1:175" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A78" s="11" t="s">
@@ -15078,10 +15173,11 @@
       <c r="CU78" s="4"/>
       <c r="CV78" s="4"/>
       <c r="CW78" s="4"/>
-      <c r="CX78" s="26"/>
+      <c r="CX78" s="4"/>
       <c r="CY78" s="26"/>
       <c r="CZ78" s="26"/>
       <c r="DA78" s="26"/>
+      <c r="DB78" s="26"/>
     </row>
     <row r="79" spans="1:175" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B79" s="8"/>
@@ -15188,7 +15284,7 @@
       <c r="CY79" s="7"/>
       <c r="CZ79" s="7"/>
       <c r="DA79" s="7"/>
-      <c r="DB79" s="20"/>
+      <c r="DB79" s="7"/>
       <c r="DC79" s="20"/>
       <c r="DD79" s="20"/>
       <c r="DE79" s="20"/>
@@ -15364,7 +15460,7 @@
       <c r="CY80" s="19"/>
       <c r="CZ80" s="19"/>
       <c r="DA80" s="19"/>
-      <c r="DB80" s="20"/>
+      <c r="DB80" s="19"/>
       <c r="DC80" s="20"/>
       <c r="DD80" s="20"/>
       <c r="DE80" s="20"/>
@@ -15543,6 +15639,7 @@
       <c r="CY81" s="26"/>
       <c r="CZ81" s="26"/>
       <c r="DA81" s="26"/>
+      <c r="DB81" s="26"/>
     </row>
     <row r="82" spans="1:179" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A82" s="4" t="s">
@@ -15652,6 +15749,7 @@
       <c r="CY82" s="26"/>
       <c r="CZ82" s="26"/>
       <c r="DA82" s="26"/>
+      <c r="DB82" s="26"/>
     </row>
     <row r="83" spans="1:179" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A83" s="4"/>
@@ -15759,6 +15857,7 @@
       <c r="CY83" s="26"/>
       <c r="CZ83" s="26"/>
       <c r="DA83" s="26"/>
+      <c r="DB83" s="26"/>
     </row>
     <row r="84" spans="1:179" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A84" s="4" t="s">
@@ -15868,6 +15967,7 @@
       <c r="CY84" s="26"/>
       <c r="CZ84" s="26"/>
       <c r="DA84" s="26"/>
+      <c r="DB84" s="26"/>
     </row>
     <row r="85" spans="1:179" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A85" s="4" t="s">
@@ -15977,6 +16077,7 @@
       <c r="CY85" s="26"/>
       <c r="CZ85" s="26"/>
       <c r="DA85" s="26"/>
+      <c r="DB85" s="26"/>
     </row>
     <row r="86" spans="1:179" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A86" s="4" t="s">
@@ -16086,6 +16187,7 @@
       <c r="CY86" s="4"/>
       <c r="CZ86" s="4"/>
       <c r="DA86" s="4"/>
+      <c r="DB86" s="4"/>
     </row>
     <row r="87" spans="1:179" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A87" s="4"/>
@@ -16193,6 +16295,7 @@
       <c r="CY87" s="4"/>
       <c r="CZ87" s="4"/>
       <c r="DA87" s="4"/>
+      <c r="DB87" s="4"/>
     </row>
     <row r="88" spans="1:179" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A88" s="15"/>
@@ -16352,6 +16455,9 @@
       <c r="CY88" s="24"/>
       <c r="CZ88" s="24"/>
       <c r="DA88" s="24"/>
+      <c r="DB88" s="24">
+        <v>2026</v>
+      </c>
     </row>
     <row r="89" spans="1:179" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A89" s="5" t="s">
@@ -16668,6 +16774,9 @@
       </c>
       <c r="DA89" s="12" t="s">
         <v>5</v>
+      </c>
+      <c r="DB89" s="12" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="90" spans="1:179" s="18" customFormat="1" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -16776,6 +16885,7 @@
       <c r="CY90" s="4"/>
       <c r="CZ90" s="4"/>
       <c r="DA90" s="4"/>
+      <c r="DB90" s="4"/>
     </row>
     <row r="91" spans="1:179" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="4" t="s">
@@ -17093,7 +17203,9 @@
       <c r="DA91" s="14">
         <v>144.09413784347819</v>
       </c>
-      <c r="DB91" s="20"/>
+      <c r="DB91" s="14">
+        <v>122.50783516602633</v>
+      </c>
       <c r="DC91" s="20"/>
       <c r="DD91" s="20"/>
       <c r="DE91" s="20"/>
@@ -17484,7 +17596,9 @@
       <c r="DA92" s="14">
         <v>138.87052204122486</v>
       </c>
-      <c r="DB92" s="20"/>
+      <c r="DB92" s="14">
+        <v>113.83023005825541</v>
+      </c>
       <c r="DC92" s="20"/>
       <c r="DD92" s="20"/>
       <c r="DE92" s="20"/>
@@ -17875,7 +17989,9 @@
       <c r="DA93" s="14">
         <v>150.09139621342192</v>
       </c>
-      <c r="DB93" s="20"/>
+      <c r="DB93" s="14">
+        <v>120.15751852344485</v>
+      </c>
       <c r="DC93" s="20"/>
       <c r="DD93" s="20"/>
       <c r="DE93" s="20"/>
@@ -18055,7 +18171,7 @@
       <c r="CY94" s="8"/>
       <c r="CZ94" s="8"/>
       <c r="DA94" s="8"/>
-      <c r="DB94" s="20"/>
+      <c r="DB94" s="8"/>
       <c r="DC94" s="20"/>
       <c r="DD94" s="20"/>
       <c r="DE94" s="20"/>
@@ -18446,7 +18562,9 @@
       <c r="DA95" s="14">
         <v>141.60762025518059</v>
       </c>
-      <c r="DB95" s="20"/>
+      <c r="DB95" s="14">
+        <v>117.07960867918344</v>
+      </c>
       <c r="DC95" s="20"/>
       <c r="DD95" s="20"/>
       <c r="DE95" s="20"/>
@@ -18627,6 +18745,7 @@
       <c r="CY96" s="10"/>
       <c r="CZ96" s="10"/>
       <c r="DA96" s="10"/>
+      <c r="DB96" s="10"/>
     </row>
     <row r="97" spans="1:179" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A97" s="11" t="s">
@@ -18736,6 +18855,7 @@
       <c r="CY97" s="4"/>
       <c r="CZ97" s="4"/>
       <c r="DA97" s="4"/>
+      <c r="DB97" s="4"/>
     </row>
     <row r="98" spans="1:179" x14ac:dyDescent="0.25">
       <c r="B98" s="4"/>
@@ -18842,6 +18962,7 @@
       <c r="CY98" s="4"/>
       <c r="CZ98" s="4"/>
       <c r="DA98" s="4"/>
+      <c r="DB98" s="4"/>
     </row>
     <row r="99" spans="1:179" x14ac:dyDescent="0.25">
       <c r="B99" s="4"/>
@@ -18948,6 +19069,7 @@
       <c r="CY99" s="4"/>
       <c r="CZ99" s="4"/>
       <c r="DA99" s="4"/>
+      <c r="DB99" s="4"/>
     </row>
     <row r="100" spans="1:179" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A100" s="4" t="s">
@@ -19057,6 +19179,7 @@
       <c r="CY100" s="4"/>
       <c r="CZ100" s="4"/>
       <c r="DA100" s="4"/>
+      <c r="DB100" s="4"/>
     </row>
     <row r="101" spans="1:179" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A101" s="4" t="s">
@@ -19166,6 +19289,7 @@
       <c r="CY101" s="4"/>
       <c r="CZ101" s="4"/>
       <c r="DA101" s="4"/>
+      <c r="DB101" s="4"/>
     </row>
     <row r="102" spans="1:179" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A102" s="4" t="s">
@@ -19275,6 +19399,7 @@
       <c r="CY102" s="4"/>
       <c r="CZ102" s="4"/>
       <c r="DA102" s="4"/>
+      <c r="DB102" s="4"/>
     </row>
     <row r="103" spans="1:179" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A103" s="4"/>
@@ -19382,6 +19507,7 @@
       <c r="CY103" s="4"/>
       <c r="CZ103" s="4"/>
       <c r="DA103" s="4"/>
+      <c r="DB103" s="4"/>
     </row>
     <row r="104" spans="1:179" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A104" s="4" t="s">
@@ -19491,6 +19617,7 @@
       <c r="CY104" s="4"/>
       <c r="CZ104" s="4"/>
       <c r="DA104" s="4"/>
+      <c r="DB104" s="4"/>
     </row>
     <row r="105" spans="1:179" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A105" s="4" t="s">
@@ -19600,6 +19727,7 @@
       <c r="CY105" s="4"/>
       <c r="CZ105" s="4"/>
       <c r="DA105" s="4"/>
+      <c r="DB105" s="4"/>
     </row>
     <row r="106" spans="1:179" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A106" s="4" t="s">
@@ -19709,6 +19837,7 @@
       <c r="CY106" s="4"/>
       <c r="CZ106" s="4"/>
       <c r="DA106" s="4"/>
+      <c r="DB106" s="4"/>
     </row>
     <row r="107" spans="1:179" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A107" s="4"/>
@@ -19816,6 +19945,7 @@
       <c r="CY107" s="4"/>
       <c r="CZ107" s="4"/>
       <c r="DA107" s="4"/>
+      <c r="DB107" s="4"/>
     </row>
     <row r="108" spans="1:179" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A108" s="15"/>
@@ -19975,6 +20105,9 @@
       <c r="CY108" s="24"/>
       <c r="CZ108" s="24"/>
       <c r="DA108" s="24"/>
+      <c r="DB108" s="24">
+        <v>2026</v>
+      </c>
     </row>
     <row r="109" spans="1:179" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A109" s="5" t="s">
@@ -20291,6 +20424,9 @@
       </c>
       <c r="DA109" s="12" t="s">
         <v>5</v>
+      </c>
+      <c r="DB109" s="12" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="110" spans="1:179" s="18" customFormat="1" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -20399,6 +20535,7 @@
       <c r="CY110" s="4"/>
       <c r="CZ110" s="4"/>
       <c r="DA110" s="4"/>
+      <c r="DB110" s="4"/>
     </row>
     <row r="111" spans="1:179" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="4" t="s">
@@ -20716,7 +20853,9 @@
       <c r="DA111" s="14">
         <v>38.873313289402567</v>
       </c>
-      <c r="DB111" s="20"/>
+      <c r="DB111" s="14">
+        <v>35.516443405310717</v>
+      </c>
       <c r="DC111" s="20"/>
       <c r="DD111" s="20"/>
       <c r="DE111" s="20"/>
@@ -21107,7 +21246,9 @@
       <c r="DA112" s="14">
         <v>54.122131323881895</v>
       </c>
-      <c r="DB112" s="20"/>
+      <c r="DB112" s="14">
+        <v>59.553280997797216</v>
+      </c>
       <c r="DC112" s="20"/>
       <c r="DD112" s="20"/>
       <c r="DE112" s="20"/>
@@ -21498,7 +21639,9 @@
       <c r="DA113" s="14">
         <v>7.0045553867155288</v>
       </c>
-      <c r="DB113" s="20"/>
+      <c r="DB113" s="14">
+        <v>4.9302755968920673</v>
+      </c>
       <c r="DC113" s="20"/>
       <c r="DD113" s="20"/>
       <c r="DE113" s="20"/>
@@ -21678,7 +21821,7 @@
       <c r="CY114" s="8"/>
       <c r="CZ114" s="8"/>
       <c r="DA114" s="8"/>
-      <c r="DB114" s="20"/>
+      <c r="DB114" s="8"/>
       <c r="DC114" s="20"/>
       <c r="DD114" s="20"/>
       <c r="DE114" s="20"/>
@@ -22069,7 +22212,9 @@
       <c r="DA115" s="14">
         <v>100</v>
       </c>
-      <c r="DB115" s="20"/>
+      <c r="DB115" s="14">
+        <v>100</v>
+      </c>
       <c r="DC115" s="20"/>
       <c r="DD115" s="20"/>
       <c r="DE115" s="20"/>
@@ -22250,6 +22395,7 @@
       <c r="CY116" s="10"/>
       <c r="CZ116" s="10"/>
       <c r="DA116" s="10"/>
+      <c r="DB116" s="10"/>
     </row>
     <row r="117" spans="1:179" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A117" s="11" t="s">
@@ -22359,6 +22505,7 @@
       <c r="CY117" s="4"/>
       <c r="CZ117" s="4"/>
       <c r="DA117" s="4"/>
+      <c r="DB117" s="4"/>
     </row>
     <row r="118" spans="1:179" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B118" s="8"/>
@@ -22465,7 +22612,7 @@
       <c r="CY118" s="8"/>
       <c r="CZ118" s="8"/>
       <c r="DA118" s="8"/>
-      <c r="DB118" s="20"/>
+      <c r="DB118" s="8"/>
       <c r="DC118" s="20"/>
       <c r="DD118" s="20"/>
       <c r="DE118" s="20"/>
@@ -22645,7 +22792,7 @@
       <c r="CY119" s="8"/>
       <c r="CZ119" s="8"/>
       <c r="DA119" s="8"/>
-      <c r="DB119" s="20"/>
+      <c r="DB119" s="8"/>
       <c r="DC119" s="20"/>
       <c r="DD119" s="20"/>
       <c r="DE119" s="20"/>
@@ -22828,6 +22975,7 @@
       <c r="CY120" s="4"/>
       <c r="CZ120" s="4"/>
       <c r="DA120" s="4"/>
+      <c r="DB120" s="4"/>
     </row>
     <row r="121" spans="1:179" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A121" s="4" t="s">
@@ -22937,6 +23085,7 @@
       <c r="CY121" s="4"/>
       <c r="CZ121" s="4"/>
       <c r="DA121" s="4"/>
+      <c r="DB121" s="4"/>
     </row>
     <row r="122" spans="1:179" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A122" s="4" t="s">
@@ -23046,6 +23195,7 @@
       <c r="CY122" s="4"/>
       <c r="CZ122" s="4"/>
       <c r="DA122" s="4"/>
+      <c r="DB122" s="4"/>
     </row>
     <row r="123" spans="1:179" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A123" s="4"/>
@@ -23153,6 +23303,7 @@
       <c r="CY123" s="4"/>
       <c r="CZ123" s="4"/>
       <c r="DA123" s="4"/>
+      <c r="DB123" s="4"/>
     </row>
     <row r="124" spans="1:179" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A124" s="4" t="s">
@@ -23262,6 +23413,7 @@
       <c r="CY124" s="4"/>
       <c r="CZ124" s="4"/>
       <c r="DA124" s="4"/>
+      <c r="DB124" s="4"/>
     </row>
     <row r="125" spans="1:179" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A125" s="4" t="s">
@@ -23371,6 +23523,7 @@
       <c r="CY125" s="4"/>
       <c r="CZ125" s="4"/>
       <c r="DA125" s="4"/>
+      <c r="DB125" s="4"/>
     </row>
     <row r="126" spans="1:179" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A126" s="4" t="s">
@@ -23480,6 +23633,7 @@
       <c r="CY126" s="4"/>
       <c r="CZ126" s="4"/>
       <c r="DA126" s="4"/>
+      <c r="DB126" s="4"/>
     </row>
     <row r="127" spans="1:179" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A127" s="4"/>
@@ -23587,6 +23741,7 @@
       <c r="CY127" s="4"/>
       <c r="CZ127" s="4"/>
       <c r="DA127" s="4"/>
+      <c r="DB127" s="4"/>
     </row>
     <row r="128" spans="1:179" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A128" s="15"/>
@@ -23746,6 +23901,9 @@
       <c r="CY128" s="24"/>
       <c r="CZ128" s="24"/>
       <c r="DA128" s="24"/>
+      <c r="DB128" s="24">
+        <v>2026</v>
+      </c>
     </row>
     <row r="129" spans="1:179" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A129" s="5" t="s">
@@ -24062,6 +24220,9 @@
       </c>
       <c r="DA129" s="12" t="s">
         <v>5</v>
+      </c>
+      <c r="DB129" s="12" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="130" spans="1:179" s="18" customFormat="1" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -24170,6 +24331,7 @@
       <c r="CY130" s="4"/>
       <c r="CZ130" s="4"/>
       <c r="DA130" s="4"/>
+      <c r="DB130" s="4"/>
     </row>
     <row r="131" spans="1:179" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A131" s="4" t="s">
@@ -24487,7 +24649,9 @@
       <c r="DA131" s="14">
         <v>38.202507532443192</v>
       </c>
-      <c r="DB131" s="20"/>
+      <c r="DB131" s="14">
+        <v>33.942737539478642</v>
+      </c>
       <c r="DC131" s="20"/>
       <c r="DD131" s="20"/>
       <c r="DE131" s="20"/>
@@ -24878,7 +25042,9 @@
       <c r="DA132" s="14">
         <v>55.188863030543864</v>
       </c>
-      <c r="DB132" s="20"/>
+      <c r="DB132" s="14">
+        <v>61.253278950725246</v>
+      </c>
       <c r="DC132" s="20"/>
       <c r="DD132" s="20"/>
       <c r="DE132" s="20"/>
@@ -25269,7 +25435,9 @@
       <c r="DA133" s="14">
         <v>6.6086294370129375</v>
       </c>
-      <c r="DB133" s="20"/>
+      <c r="DB133" s="14">
+        <v>4.8039835097961188</v>
+      </c>
       <c r="DC133" s="20"/>
       <c r="DD133" s="20"/>
       <c r="DE133" s="20"/>
@@ -25449,7 +25617,7 @@
       <c r="CY134" s="8"/>
       <c r="CZ134" s="8"/>
       <c r="DA134" s="8"/>
-      <c r="DB134" s="20"/>
+      <c r="DB134" s="8"/>
       <c r="DC134" s="20"/>
       <c r="DD134" s="20"/>
       <c r="DE134" s="20"/>
@@ -25840,7 +26008,9 @@
       <c r="DA135" s="14">
         <v>100</v>
       </c>
-      <c r="DB135" s="20"/>
+      <c r="DB135" s="14">
+        <v>100</v>
+      </c>
       <c r="DC135" s="20"/>
       <c r="DD135" s="20"/>
       <c r="DE135" s="20"/>
@@ -26021,6 +26191,7 @@
       <c r="CY136" s="10"/>
       <c r="CZ136" s="10"/>
       <c r="DA136" s="10"/>
+      <c r="DB136" s="10"/>
     </row>
     <row r="137" spans="1:179" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A137" s="11" t="s">
@@ -26130,6 +26301,7 @@
       <c r="CY137" s="4"/>
       <c r="CZ137" s="4"/>
       <c r="DA137" s="4"/>
+      <c r="DB137" s="4"/>
     </row>
     <row r="138" spans="1:179" s="23" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A138" s="4"/>
@@ -26237,7 +26409,7 @@
       <c r="CY138" s="13"/>
       <c r="CZ138" s="13"/>
       <c r="DA138" s="13"/>
-      <c r="DB138" s="22"/>
+      <c r="DB138" s="13"/>
       <c r="DC138" s="22"/>
       <c r="DD138" s="22"/>
       <c r="DE138" s="22"/>
@@ -26327,9 +26499,9 @@
   <pageSetup paperSize="9" scale="48" orientation="landscape" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
   <rowBreaks count="3" manualBreakCount="3">
-    <brk id="40" max="81" man="1"/>
-    <brk id="80" max="81" man="1"/>
-    <brk id="99" max="81" man="1"/>
+    <brk id="40" max="105" man="1"/>
+    <brk id="80" max="105" man="1"/>
+    <brk id="99" max="105" man="1"/>
   </rowBreaks>
 </worksheet>
 </file>
--- a/Data/National Accounts/PSA-20HHSW_2018PSNA_Qrt.xlsx
+++ b/Data/National Accounts/PSA-20HHSW_2018PSNA_Qrt.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Shared drives\QNAP\NAP Dissemination\As of May 2026\Tables\NAP Q1 2000 to Q1 2026\Qtr\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Shared drives\QNAP\NAP Dissemination\As of August 2026\Tables\NAP Q1 2000 to Q2 2026\Qtr\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5490CE1-7F2D-4964-B94B-8C726F4E5616}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E15DE99-0372-4494-BAC4-FB4235377D4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="794" xr2:uid="{736930C2-BFBB-46C3-AE9E-AECFC8C3145D}"/>
   </bookViews>
@@ -356,7 +356,7 @@
     <definedName name="pet">#REF!</definedName>
     <definedName name="plastic">#REF!</definedName>
     <definedName name="ply">#REF!</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">HHSW!$A$1:$DB$138</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">HHSW!$A$1:$DC$138</definedName>
     <definedName name="_xlnm.Print_Area">#REF!</definedName>
     <definedName name="PRINT_AREA_MI">#REF!</definedName>
     <definedName name="Print_Titles_MI">#REF!,#REF!</definedName>
@@ -530,7 +530,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="862" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="869" uniqueCount="55">
   <si>
     <t>National Accounts of the Philippines</t>
   </si>
@@ -689,13 +689,13 @@
     <t>Table 21.7 Gross Value Added in Human Health and Social Work Activities, by Industry</t>
   </si>
   <si>
-    <t>Q1 2000 to Q1 2026</t>
+    <t>2025 - 2026</t>
   </si>
   <si>
-    <t>As of May 2026</t>
+    <t>Q1 2000 to Q2 2026</t>
   </si>
   <si>
-    <t>2025 - 2026</t>
+    <t>As of August 2026</t>
   </si>
 </sst>
 </file>
@@ -1218,8 +1218,8 @@
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="49.28515625" style="4" customWidth="1"/>
-    <col min="2" max="106" width="13" style="21" customWidth="1"/>
-    <col min="107" max="16384" width="10" style="21"/>
+    <col min="2" max="107" width="13" style="21" customWidth="1"/>
+    <col min="108" max="16384" width="10" style="21"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:179" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.2">
@@ -1234,7 +1234,7 @@
     </row>
     <row r="3" spans="1:179" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="4" spans="1:179" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.2">
@@ -1247,7 +1247,7 @@
     </row>
     <row r="6" spans="1:179" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="7" spans="1:179" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.2">
@@ -1362,6 +1362,7 @@
       <c r="CZ8" s="4"/>
       <c r="DA8" s="4"/>
       <c r="DB8" s="4"/>
+      <c r="DC8" s="4"/>
     </row>
     <row r="9" spans="1:179" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A9" s="15"/>
@@ -1524,6 +1525,7 @@
       <c r="DB9" s="24">
         <v>2026</v>
       </c>
+      <c r="DC9" s="24"/>
     </row>
     <row r="10" spans="1:179" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
@@ -1843,6 +1845,9 @@
       </c>
       <c r="DB10" s="12" t="s">
         <v>2</v>
+      </c>
+      <c r="DC10" s="12" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:179" s="18" customFormat="1" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -1952,6 +1957,7 @@
       <c r="CZ11" s="4"/>
       <c r="DA11" s="4"/>
       <c r="DB11" s="4"/>
+      <c r="DC11" s="4"/>
     </row>
     <row r="12" spans="1:179" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
@@ -2272,7 +2278,9 @@
       <c r="DB12" s="25">
         <v>53351.656396032027</v>
       </c>
-      <c r="DC12" s="20"/>
+      <c r="DC12" s="25">
+        <v>33591.764850212043</v>
+      </c>
       <c r="DD12" s="20"/>
       <c r="DE12" s="20"/>
       <c r="DF12" s="20"/>
@@ -2663,9 +2671,11 @@
         <v>99023.154657254374</v>
       </c>
       <c r="DB13" s="25">
-        <v>89459.018989939999</v>
-      </c>
-      <c r="DC13" s="20"/>
+        <v>90075.309664854343</v>
+      </c>
+      <c r="DC13" s="25">
+        <v>112969.35808894694</v>
+      </c>
       <c r="DD13" s="20"/>
       <c r="DE13" s="20"/>
       <c r="DF13" s="20"/>
@@ -3058,7 +3068,9 @@
       <c r="DB14" s="25">
         <v>7406.1010721528382</v>
       </c>
-      <c r="DC14" s="20"/>
+      <c r="DC14" s="25">
+        <v>5383.5804939984846</v>
+      </c>
       <c r="DD14" s="20"/>
       <c r="DE14" s="20"/>
       <c r="DF14" s="20"/>
@@ -3238,7 +3250,7 @@
       <c r="CZ15" s="8"/>
       <c r="DA15" s="8"/>
       <c r="DB15" s="8"/>
-      <c r="DC15" s="20"/>
+      <c r="DC15" s="8"/>
       <c r="DD15" s="20"/>
       <c r="DE15" s="20"/>
       <c r="DF15" s="20"/>
@@ -3629,9 +3641,11 @@
         <v>182962.40786356371</v>
       </c>
       <c r="DB16" s="17">
-        <v>150216.77645812486</v>
-      </c>
-      <c r="DC16" s="20"/>
+        <v>150833.06713303921</v>
+      </c>
+      <c r="DC16" s="17">
+        <v>151944.70343315747</v>
+      </c>
       <c r="DD16" s="20"/>
       <c r="DE16" s="20"/>
       <c r="DF16" s="20"/>
@@ -3812,6 +3826,7 @@
       <c r="CZ17" s="10"/>
       <c r="DA17" s="10"/>
       <c r="DB17" s="10"/>
+      <c r="DC17" s="10"/>
     </row>
     <row r="18" spans="1:179" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A18" s="11" t="s">
@@ -3922,6 +3937,7 @@
       <c r="CZ18" s="4"/>
       <c r="DA18" s="4"/>
       <c r="DB18" s="4"/>
+      <c r="DC18" s="4"/>
     </row>
     <row r="19" spans="1:179" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="8"/>
@@ -4029,7 +4045,7 @@
       <c r="CZ19" s="8"/>
       <c r="DA19" s="8"/>
       <c r="DB19" s="8"/>
-      <c r="DC19" s="20"/>
+      <c r="DC19" s="8"/>
       <c r="DD19" s="20"/>
       <c r="DE19" s="20"/>
       <c r="DF19" s="20"/>
@@ -4209,7 +4225,7 @@
       <c r="CZ20" s="8"/>
       <c r="DA20" s="8"/>
       <c r="DB20" s="8"/>
-      <c r="DC20" s="20"/>
+      <c r="DC20" s="8"/>
       <c r="DD20" s="20"/>
       <c r="DE20" s="20"/>
       <c r="DF20" s="20"/>
@@ -4392,6 +4408,7 @@
       <c r="CZ21" s="4"/>
       <c r="DA21" s="4"/>
       <c r="DB21" s="4"/>
+      <c r="DC21" s="4"/>
     </row>
     <row r="22" spans="1:179" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
@@ -4502,10 +4519,11 @@
       <c r="CZ22" s="4"/>
       <c r="DA22" s="4"/>
       <c r="DB22" s="4"/>
+      <c r="DC22" s="4"/>
     </row>
     <row r="23" spans="1:179" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A23" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B23" s="4"/>
       <c r="C23" s="4"/>
@@ -4612,6 +4630,7 @@
       <c r="CZ23" s="4"/>
       <c r="DA23" s="4"/>
       <c r="DB23" s="4"/>
+      <c r="DC23" s="4"/>
     </row>
     <row r="24" spans="1:179" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A24" s="4"/>
@@ -4720,6 +4739,7 @@
       <c r="CZ24" s="4"/>
       <c r="DA24" s="4"/>
       <c r="DB24" s="4"/>
+      <c r="DC24" s="4"/>
     </row>
     <row r="25" spans="1:179" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A25" s="4" t="s">
@@ -4830,10 +4850,11 @@
       <c r="CZ25" s="4"/>
       <c r="DA25" s="4"/>
       <c r="DB25" s="4"/>
+      <c r="DC25" s="4"/>
     </row>
     <row r="26" spans="1:179" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A26" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B26" s="4"/>
       <c r="C26" s="4"/>
@@ -4940,6 +4961,7 @@
       <c r="CZ26" s="4"/>
       <c r="DA26" s="4"/>
       <c r="DB26" s="4"/>
+      <c r="DC26" s="4"/>
     </row>
     <row r="27" spans="1:179" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A27" s="4" t="s">
@@ -5050,6 +5072,7 @@
       <c r="CZ27" s="4"/>
       <c r="DA27" s="4"/>
       <c r="DB27" s="4"/>
+      <c r="DC27" s="4"/>
     </row>
     <row r="28" spans="1:179" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A28" s="4"/>
@@ -5158,6 +5181,7 @@
       <c r="CZ28" s="4"/>
       <c r="DA28" s="4"/>
       <c r="DB28" s="4"/>
+      <c r="DC28" s="4"/>
     </row>
     <row r="29" spans="1:179" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A29" s="15"/>
@@ -5320,6 +5344,7 @@
       <c r="DB29" s="24">
         <v>2026</v>
       </c>
+      <c r="DC29" s="24"/>
     </row>
     <row r="30" spans="1:179" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A30" s="5" t="s">
@@ -5639,6 +5664,9 @@
       </c>
       <c r="DB30" s="12" t="s">
         <v>2</v>
+      </c>
+      <c r="DC30" s="12" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="31" spans="1:179" s="18" customFormat="1" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -5748,6 +5776,7 @@
       <c r="CZ31" s="4"/>
       <c r="DA31" s="4"/>
       <c r="DB31" s="4"/>
+      <c r="DC31" s="4"/>
     </row>
     <row r="32" spans="1:179" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="4" t="s">
@@ -6068,7 +6097,9 @@
       <c r="DB32" s="25">
         <v>43549.587113124842</v>
       </c>
-      <c r="DC32" s="20"/>
+      <c r="DC32" s="25">
+        <v>27199.55848365002</v>
+      </c>
       <c r="DD32" s="20"/>
       <c r="DE32" s="20"/>
       <c r="DF32" s="20"/>
@@ -6459,9 +6490,11 @@
         <v>71306.100964939513</v>
       </c>
       <c r="DB33" s="25">
-        <v>78589.860482718126</v>
-      </c>
-      <c r="DC33" s="20"/>
+        <v>79131.272614274843</v>
+      </c>
+      <c r="DC33" s="25">
+        <v>90641.439075736416</v>
+      </c>
       <c r="DD33" s="20"/>
       <c r="DE33" s="20"/>
       <c r="DF33" s="20"/>
@@ -6854,7 +6887,9 @@
       <c r="DB34" s="25">
         <v>6163.6601380942939</v>
       </c>
-      <c r="DC34" s="20"/>
+      <c r="DC34" s="25">
+        <v>4183.7871056865852</v>
+      </c>
       <c r="DD34" s="20"/>
       <c r="DE34" s="20"/>
       <c r="DF34" s="20"/>
@@ -7034,7 +7069,7 @@
       <c r="CZ35" s="8"/>
       <c r="DA35" s="8"/>
       <c r="DB35" s="8"/>
-      <c r="DC35" s="20"/>
+      <c r="DC35" s="8"/>
       <c r="DD35" s="20"/>
       <c r="DE35" s="20"/>
       <c r="DF35" s="20"/>
@@ -7425,9 +7460,11 @@
         <v>129203.7868681507</v>
       </c>
       <c r="DB36" s="17">
-        <v>128303.10773393726</v>
-      </c>
-      <c r="DC36" s="20"/>
+        <v>128844.51986549397</v>
+      </c>
+      <c r="DC36" s="17">
+        <v>122024.78466507302</v>
+      </c>
       <c r="DD36" s="20"/>
       <c r="DE36" s="20"/>
       <c r="DF36" s="20"/>
@@ -7608,6 +7645,7 @@
       <c r="CZ37" s="10"/>
       <c r="DA37" s="10"/>
       <c r="DB37" s="10"/>
+      <c r="DC37" s="10"/>
     </row>
     <row r="38" spans="1:179" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A38" s="11" t="s">
@@ -7718,6 +7756,7 @@
       <c r="CZ38" s="4"/>
       <c r="DA38" s="4"/>
       <c r="DB38" s="4"/>
+      <c r="DC38" s="4"/>
     </row>
     <row r="39" spans="1:179" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B39" s="8"/>
@@ -7825,7 +7864,7 @@
       <c r="CZ39" s="7"/>
       <c r="DA39" s="7"/>
       <c r="DB39" s="7"/>
-      <c r="DC39" s="20"/>
+      <c r="DC39" s="7"/>
       <c r="DD39" s="20"/>
       <c r="DE39" s="20"/>
       <c r="DF39" s="20"/>
@@ -8005,7 +8044,7 @@
       <c r="CZ40" s="7"/>
       <c r="DA40" s="7"/>
       <c r="DB40" s="7"/>
-      <c r="DC40" s="20"/>
+      <c r="DC40" s="7"/>
       <c r="DD40" s="20"/>
       <c r="DE40" s="20"/>
       <c r="DF40" s="20"/>
@@ -8188,6 +8227,7 @@
       <c r="CZ41" s="26"/>
       <c r="DA41" s="26"/>
       <c r="DB41" s="26"/>
+      <c r="DC41" s="26"/>
     </row>
     <row r="42" spans="1:179" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A42" s="4" t="s">
@@ -8298,10 +8338,11 @@
       <c r="CZ42" s="26"/>
       <c r="DA42" s="26"/>
       <c r="DB42" s="26"/>
+      <c r="DC42" s="26"/>
     </row>
     <row r="43" spans="1:179" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A43" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B43" s="4"/>
       <c r="C43" s="4"/>
@@ -8408,6 +8449,7 @@
       <c r="CZ43" s="26"/>
       <c r="DA43" s="26"/>
       <c r="DB43" s="26"/>
+      <c r="DC43" s="26"/>
     </row>
     <row r="44" spans="1:179" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A44" s="4"/>
@@ -8516,6 +8558,7 @@
       <c r="CZ44" s="26"/>
       <c r="DA44" s="26"/>
       <c r="DB44" s="26"/>
+      <c r="DC44" s="26"/>
     </row>
     <row r="45" spans="1:179" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A45" s="4" t="s">
@@ -8626,10 +8669,11 @@
       <c r="CZ45" s="26"/>
       <c r="DA45" s="26"/>
       <c r="DB45" s="26"/>
+      <c r="DC45" s="26"/>
     </row>
     <row r="46" spans="1:179" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B46" s="4"/>
       <c r="C46" s="4"/>
@@ -8736,6 +8780,7 @@
       <c r="CZ46" s="26"/>
       <c r="DA46" s="26"/>
       <c r="DB46" s="26"/>
+      <c r="DC46" s="26"/>
     </row>
     <row r="47" spans="1:179" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A47" s="4" t="s">
@@ -8846,6 +8891,7 @@
       <c r="CZ47" s="26"/>
       <c r="DA47" s="26"/>
       <c r="DB47" s="26"/>
+      <c r="DC47" s="26"/>
     </row>
     <row r="48" spans="1:179" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A48" s="4"/>
@@ -8950,10 +8996,11 @@
       <c r="CV48" s="4"/>
       <c r="CW48" s="4"/>
       <c r="CX48" s="4"/>
-      <c r="CY48" s="26"/>
+      <c r="CY48" s="4"/>
       <c r="CZ48" s="26"/>
       <c r="DA48" s="26"/>
       <c r="DB48" s="26"/>
+      <c r="DC48" s="26"/>
     </row>
     <row r="49" spans="1:175" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A49" s="15"/>
@@ -9108,12 +9155,13 @@
       <c r="CV49" s="24"/>
       <c r="CW49" s="24"/>
       <c r="CX49" s="24" t="s">
-        <v>54</v>
-      </c>
-      <c r="CY49" s="27"/>
+        <v>52</v>
+      </c>
+      <c r="CY49" s="24"/>
       <c r="CZ49" s="27"/>
       <c r="DA49" s="27"/>
       <c r="DB49" s="27"/>
+      <c r="DC49" s="27"/>
     </row>
     <row r="50" spans="1:175" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A50" s="5" t="s">
@@ -9422,10 +9470,13 @@
       <c r="CX50" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="CY50" s="28"/>
+      <c r="CY50" s="5" t="s">
+        <v>3</v>
+      </c>
       <c r="CZ50" s="28"/>
       <c r="DA50" s="28"/>
       <c r="DB50" s="28"/>
+      <c r="DC50" s="28"/>
     </row>
     <row r="51" spans="1:175" s="18" customFormat="1" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="6"/>
@@ -9530,10 +9581,11 @@
       <c r="CV51" s="4"/>
       <c r="CW51" s="4"/>
       <c r="CX51" s="4"/>
-      <c r="CY51" s="26"/>
+      <c r="CY51" s="4"/>
       <c r="CZ51" s="26"/>
       <c r="DA51" s="26"/>
       <c r="DB51" s="26"/>
+      <c r="DC51" s="26"/>
     </row>
     <row r="52" spans="1:175" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="4" t="s">
@@ -9842,11 +9894,13 @@
       <c r="CX52" s="14">
         <v>8.2063011949943956</v>
       </c>
-      <c r="CY52" s="16"/>
+      <c r="CY52" s="14">
+        <v>12.123517623052393</v>
+      </c>
       <c r="CZ52" s="16"/>
       <c r="DA52" s="16"/>
       <c r="DB52" s="16"/>
-      <c r="DC52" s="20"/>
+      <c r="DC52" s="16"/>
       <c r="DD52" s="20"/>
       <c r="DE52" s="20"/>
       <c r="DF52" s="20"/>
@@ -10221,13 +10275,15 @@
         <v>16.719287968455077</v>
       </c>
       <c r="CX53" s="14">
-        <v>12.692519471098223</v>
-      </c>
-      <c r="CY53" s="16"/>
+        <v>13.468867676866608</v>
+      </c>
+      <c r="CY53" s="14">
+        <v>16.013109866234117</v>
+      </c>
       <c r="CZ53" s="16"/>
       <c r="DA53" s="16"/>
       <c r="DB53" s="16"/>
-      <c r="DC53" s="20"/>
+      <c r="DC53" s="16"/>
       <c r="DD53" s="20"/>
       <c r="DE53" s="20"/>
       <c r="DF53" s="20"/>
@@ -10604,11 +10660,13 @@
       <c r="CX54" s="14">
         <v>4.3420103636321272</v>
       </c>
-      <c r="CY54" s="16"/>
+      <c r="CY54" s="14">
+        <v>5.9539701777814997</v>
+      </c>
       <c r="CZ54" s="16"/>
       <c r="DA54" s="16"/>
       <c r="DB54" s="16"/>
-      <c r="DC54" s="20"/>
+      <c r="DC54" s="16"/>
       <c r="DD54" s="20"/>
       <c r="DE54" s="20"/>
       <c r="DF54" s="20"/>
@@ -10780,11 +10838,11 @@
       <c r="CV55" s="8"/>
       <c r="CW55" s="8"/>
       <c r="CX55" s="8"/>
-      <c r="CY55" s="7"/>
+      <c r="CY55" s="8"/>
       <c r="CZ55" s="7"/>
       <c r="DA55" s="7"/>
       <c r="DB55" s="7"/>
-      <c r="DC55" s="20"/>
+      <c r="DC55" s="7"/>
       <c r="DD55" s="20"/>
       <c r="DE55" s="20"/>
       <c r="DF55" s="20"/>
@@ -11159,13 +11217,15 @@
         <v>15.480420794292101</v>
       </c>
       <c r="CX56" s="14">
-        <v>10.627026989786501</v>
-      </c>
-      <c r="CY56" s="16"/>
+        <v>11.080893773076909</v>
+      </c>
+      <c r="CY56" s="14">
+        <v>14.74709673650429</v>
+      </c>
       <c r="CZ56" s="16"/>
       <c r="DA56" s="16"/>
       <c r="DB56" s="16"/>
-      <c r="DC56" s="20"/>
+      <c r="DC56" s="16"/>
       <c r="DD56" s="20"/>
       <c r="DE56" s="20"/>
       <c r="DF56" s="20"/>
@@ -11338,10 +11398,11 @@
       <c r="CV57" s="10"/>
       <c r="CW57" s="10"/>
       <c r="CX57" s="10"/>
-      <c r="CY57" s="29"/>
+      <c r="CY57" s="10"/>
       <c r="CZ57" s="29"/>
       <c r="DA57" s="29"/>
       <c r="DB57" s="29"/>
+      <c r="DC57" s="29"/>
     </row>
     <row r="58" spans="1:175" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A58" s="11" t="s">
@@ -11448,10 +11509,11 @@
       <c r="CV58" s="4"/>
       <c r="CW58" s="4"/>
       <c r="CX58" s="4"/>
-      <c r="CY58" s="26"/>
+      <c r="CY58" s="4"/>
       <c r="CZ58" s="26"/>
       <c r="DA58" s="26"/>
       <c r="DB58" s="26"/>
+      <c r="DC58" s="26"/>
     </row>
     <row r="59" spans="1:175" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B59" s="8"/>
@@ -11555,11 +11617,11 @@
       <c r="CV59" s="8"/>
       <c r="CW59" s="8"/>
       <c r="CX59" s="8"/>
-      <c r="CY59" s="7"/>
+      <c r="CY59" s="8"/>
       <c r="CZ59" s="7"/>
       <c r="DA59" s="7"/>
       <c r="DB59" s="7"/>
-      <c r="DC59" s="20"/>
+      <c r="DC59" s="7"/>
       <c r="DD59" s="20"/>
       <c r="DE59" s="20"/>
       <c r="DF59" s="20"/>
@@ -11731,11 +11793,11 @@
       <c r="CV60" s="8"/>
       <c r="CW60" s="8"/>
       <c r="CX60" s="8"/>
-      <c r="CY60" s="7"/>
+      <c r="CY60" s="8"/>
       <c r="CZ60" s="7"/>
       <c r="DA60" s="7"/>
       <c r="DB60" s="7"/>
-      <c r="DC60" s="20"/>
+      <c r="DC60" s="7"/>
       <c r="DD60" s="20"/>
       <c r="DE60" s="20"/>
       <c r="DF60" s="20"/>
@@ -11910,10 +11972,11 @@
       <c r="CV61" s="4"/>
       <c r="CW61" s="4"/>
       <c r="CX61" s="4"/>
-      <c r="CY61" s="26"/>
+      <c r="CY61" s="4"/>
       <c r="CZ61" s="26"/>
       <c r="DA61" s="26"/>
       <c r="DB61" s="26"/>
+      <c r="DC61" s="26"/>
     </row>
     <row r="62" spans="1:175" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A62" s="4" t="s">
@@ -12020,14 +12083,15 @@
       <c r="CV62" s="4"/>
       <c r="CW62" s="4"/>
       <c r="CX62" s="4"/>
-      <c r="CY62" s="26"/>
+      <c r="CY62" s="4"/>
       <c r="CZ62" s="26"/>
       <c r="DA62" s="26"/>
       <c r="DB62" s="26"/>
+      <c r="DC62" s="26"/>
     </row>
     <row r="63" spans="1:175" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A63" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B63" s="4"/>
       <c r="C63" s="4"/>
@@ -12130,10 +12194,11 @@
       <c r="CV63" s="4"/>
       <c r="CW63" s="4"/>
       <c r="CX63" s="4"/>
-      <c r="CY63" s="26"/>
+      <c r="CY63" s="4"/>
       <c r="CZ63" s="26"/>
       <c r="DA63" s="26"/>
       <c r="DB63" s="26"/>
+      <c r="DC63" s="26"/>
     </row>
     <row r="64" spans="1:175" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A64" s="4"/>
@@ -12238,10 +12303,11 @@
       <c r="CV64" s="4"/>
       <c r="CW64" s="4"/>
       <c r="CX64" s="4"/>
-      <c r="CY64" s="26"/>
+      <c r="CY64" s="4"/>
       <c r="CZ64" s="26"/>
       <c r="DA64" s="26"/>
       <c r="DB64" s="26"/>
+      <c r="DC64" s="26"/>
     </row>
     <row r="65" spans="1:175" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A65" s="4" t="s">
@@ -12348,14 +12414,15 @@
       <c r="CV65" s="4"/>
       <c r="CW65" s="4"/>
       <c r="CX65" s="4"/>
-      <c r="CY65" s="26"/>
+      <c r="CY65" s="4"/>
       <c r="CZ65" s="26"/>
       <c r="DA65" s="26"/>
       <c r="DB65" s="26"/>
+      <c r="DC65" s="26"/>
     </row>
     <row r="66" spans="1:175" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A66" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B66" s="4"/>
       <c r="C66" s="4"/>
@@ -12458,10 +12525,11 @@
       <c r="CV66" s="4"/>
       <c r="CW66" s="4"/>
       <c r="CX66" s="4"/>
-      <c r="CY66" s="26"/>
+      <c r="CY66" s="4"/>
       <c r="CZ66" s="26"/>
       <c r="DA66" s="26"/>
       <c r="DB66" s="26"/>
+      <c r="DC66" s="26"/>
     </row>
     <row r="67" spans="1:175" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A67" s="4" t="s">
@@ -12568,10 +12636,11 @@
       <c r="CV67" s="4"/>
       <c r="CW67" s="4"/>
       <c r="CX67" s="4"/>
-      <c r="CY67" s="26"/>
+      <c r="CY67" s="4"/>
       <c r="CZ67" s="26"/>
       <c r="DA67" s="26"/>
       <c r="DB67" s="26"/>
+      <c r="DC67" s="26"/>
     </row>
     <row r="68" spans="1:175" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A68" s="4"/>
@@ -12676,10 +12745,11 @@
       <c r="CV68" s="4"/>
       <c r="CW68" s="4"/>
       <c r="CX68" s="4"/>
-      <c r="CY68" s="26"/>
+      <c r="CY68" s="4"/>
       <c r="CZ68" s="26"/>
       <c r="DA68" s="26"/>
       <c r="DB68" s="26"/>
+      <c r="DC68" s="26"/>
     </row>
     <row r="69" spans="1:175" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A69" s="15"/>
@@ -12834,12 +12904,13 @@
       <c r="CV69" s="24"/>
       <c r="CW69" s="24"/>
       <c r="CX69" s="24" t="s">
-        <v>54</v>
-      </c>
-      <c r="CY69" s="27"/>
+        <v>52</v>
+      </c>
+      <c r="CY69" s="24"/>
       <c r="CZ69" s="27"/>
       <c r="DA69" s="27"/>
       <c r="DB69" s="27"/>
+      <c r="DC69" s="27"/>
     </row>
     <row r="70" spans="1:175" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A70" s="5" t="s">
@@ -13148,10 +13219,13 @@
       <c r="CX70" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="CY70" s="28"/>
+      <c r="CY70" s="5" t="s">
+        <v>3</v>
+      </c>
       <c r="CZ70" s="28"/>
       <c r="DA70" s="28"/>
       <c r="DB70" s="28"/>
+      <c r="DC70" s="28"/>
     </row>
     <row r="71" spans="1:175" s="18" customFormat="1" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="6"/>
@@ -13256,10 +13330,11 @@
       <c r="CV71" s="4"/>
       <c r="CW71" s="4"/>
       <c r="CX71" s="4"/>
-      <c r="CY71" s="26"/>
+      <c r="CY71" s="4"/>
       <c r="CZ71" s="26"/>
       <c r="DA71" s="26"/>
       <c r="DB71" s="26"/>
+      <c r="DC71" s="26"/>
     </row>
     <row r="72" spans="1:175" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="4" t="s">
@@ -13568,11 +13643,13 @@
       <c r="CX72" s="14">
         <v>5.934373006047295</v>
       </c>
-      <c r="CY72" s="16"/>
+      <c r="CY72" s="14">
+        <v>8.2817342862904582</v>
+      </c>
       <c r="CZ72" s="16"/>
       <c r="DA72" s="16"/>
       <c r="DB72" s="16"/>
-      <c r="DC72" s="20"/>
+      <c r="DC72" s="16"/>
       <c r="DD72" s="20"/>
       <c r="DE72" s="20"/>
       <c r="DF72" s="20"/>
@@ -13947,13 +14024,15 @@
         <v>13.112850039177971</v>
       </c>
       <c r="CX73" s="14">
-        <v>8.7639283981917373</v>
-      </c>
-      <c r="CY73" s="16"/>
+        <v>9.5132122109998392</v>
+      </c>
+      <c r="CY73" s="14">
+        <v>11.288302736362482</v>
+      </c>
       <c r="CZ73" s="16"/>
       <c r="DA73" s="16"/>
       <c r="DB73" s="16"/>
-      <c r="DC73" s="20"/>
+      <c r="DC73" s="16"/>
       <c r="DD73" s="20"/>
       <c r="DE73" s="20"/>
       <c r="DF73" s="20"/>
@@ -14330,11 +14409,13 @@
       <c r="CX74" s="14">
         <v>0.35991838673268717</v>
       </c>
-      <c r="CY74" s="16"/>
+      <c r="CY74" s="14">
+        <v>5.093106995721925</v>
+      </c>
       <c r="CZ74" s="16"/>
       <c r="DA74" s="16"/>
       <c r="DB74" s="16"/>
-      <c r="DC74" s="20"/>
+      <c r="DC74" s="16"/>
       <c r="DD74" s="20"/>
       <c r="DE74" s="20"/>
       <c r="DF74" s="20"/>
@@ -14506,11 +14587,11 @@
       <c r="CV75" s="8"/>
       <c r="CW75" s="8"/>
       <c r="CX75" s="8"/>
-      <c r="CY75" s="7"/>
+      <c r="CY75" s="8"/>
       <c r="CZ75" s="7"/>
       <c r="DA75" s="7"/>
       <c r="DB75" s="7"/>
-      <c r="DC75" s="20"/>
+      <c r="DC75" s="7"/>
       <c r="DD75" s="20"/>
       <c r="DE75" s="20"/>
       <c r="DF75" s="20"/>
@@ -14885,13 +14966,15 @@
         <v>11.395761422517054</v>
       </c>
       <c r="CX76" s="14">
-        <v>7.3587045493843704</v>
-      </c>
-      <c r="CY76" s="16"/>
+        <v>7.8117357042632136</v>
+      </c>
+      <c r="CY76" s="14">
+        <v>10.382033248290838</v>
+      </c>
       <c r="CZ76" s="16"/>
       <c r="DA76" s="16"/>
       <c r="DB76" s="16"/>
-      <c r="DC76" s="20"/>
+      <c r="DC76" s="16"/>
       <c r="DD76" s="20"/>
       <c r="DE76" s="20"/>
       <c r="DF76" s="20"/>
@@ -15064,10 +15147,11 @@
       <c r="CV77" s="10"/>
       <c r="CW77" s="10"/>
       <c r="CX77" s="10"/>
-      <c r="CY77" s="29"/>
+      <c r="CY77" s="10"/>
       <c r="CZ77" s="29"/>
       <c r="DA77" s="29"/>
       <c r="DB77" s="29"/>
+      <c r="DC77" s="29"/>
     </row>
     <row r="78" spans="1:175" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A78" s="11" t="s">
@@ -15174,10 +15258,11 @@
       <c r="CV78" s="4"/>
       <c r="CW78" s="4"/>
       <c r="CX78" s="4"/>
-      <c r="CY78" s="26"/>
+      <c r="CY78" s="4"/>
       <c r="CZ78" s="26"/>
       <c r="DA78" s="26"/>
       <c r="DB78" s="26"/>
+      <c r="DC78" s="26"/>
     </row>
     <row r="79" spans="1:175" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B79" s="8"/>
@@ -15281,11 +15366,11 @@
       <c r="CV79" s="8"/>
       <c r="CW79" s="8"/>
       <c r="CX79" s="7"/>
-      <c r="CY79" s="7"/>
+      <c r="CY79" s="8"/>
       <c r="CZ79" s="7"/>
       <c r="DA79" s="7"/>
       <c r="DB79" s="7"/>
-      <c r="DC79" s="20"/>
+      <c r="DC79" s="7"/>
       <c r="DD79" s="20"/>
       <c r="DE79" s="20"/>
       <c r="DF79" s="20"/>
@@ -15461,7 +15546,7 @@
       <c r="CZ80" s="19"/>
       <c r="DA80" s="19"/>
       <c r="DB80" s="19"/>
-      <c r="DC80" s="20"/>
+      <c r="DC80" s="19"/>
       <c r="DD80" s="20"/>
       <c r="DE80" s="20"/>
       <c r="DF80" s="20"/>
@@ -15640,10 +15725,11 @@
       <c r="CZ81" s="26"/>
       <c r="DA81" s="26"/>
       <c r="DB81" s="26"/>
+      <c r="DC81" s="26"/>
     </row>
     <row r="82" spans="1:179" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A82" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B82" s="4"/>
       <c r="C82" s="4"/>
@@ -15750,6 +15836,7 @@
       <c r="CZ82" s="26"/>
       <c r="DA82" s="26"/>
       <c r="DB82" s="26"/>
+      <c r="DC82" s="26"/>
     </row>
     <row r="83" spans="1:179" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A83" s="4"/>
@@ -15858,6 +15945,7 @@
       <c r="CZ83" s="26"/>
       <c r="DA83" s="26"/>
       <c r="DB83" s="26"/>
+      <c r="DC83" s="26"/>
     </row>
     <row r="84" spans="1:179" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A84" s="4" t="s">
@@ -15968,10 +16056,11 @@
       <c r="CZ84" s="26"/>
       <c r="DA84" s="26"/>
       <c r="DB84" s="26"/>
+      <c r="DC84" s="26"/>
     </row>
     <row r="85" spans="1:179" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A85" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B85" s="4"/>
       <c r="C85" s="4"/>
@@ -16078,6 +16167,7 @@
       <c r="CZ85" s="26"/>
       <c r="DA85" s="26"/>
       <c r="DB85" s="26"/>
+      <c r="DC85" s="26"/>
     </row>
     <row r="86" spans="1:179" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A86" s="4" t="s">
@@ -16188,6 +16278,7 @@
       <c r="CZ86" s="4"/>
       <c r="DA86" s="4"/>
       <c r="DB86" s="4"/>
+      <c r="DC86" s="4"/>
     </row>
     <row r="87" spans="1:179" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A87" s="4"/>
@@ -16296,6 +16387,7 @@
       <c r="CZ87" s="4"/>
       <c r="DA87" s="4"/>
       <c r="DB87" s="4"/>
+      <c r="DC87" s="4"/>
     </row>
     <row r="88" spans="1:179" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A88" s="15"/>
@@ -16458,6 +16550,7 @@
       <c r="DB88" s="24">
         <v>2026</v>
       </c>
+      <c r="DC88" s="24"/>
     </row>
     <row r="89" spans="1:179" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A89" s="5" t="s">
@@ -16777,6 +16870,9 @@
       </c>
       <c r="DB89" s="12" t="s">
         <v>2</v>
+      </c>
+      <c r="DC89" s="12" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="90" spans="1:179" s="18" customFormat="1" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -16886,6 +16982,7 @@
       <c r="CZ90" s="4"/>
       <c r="DA90" s="4"/>
       <c r="DB90" s="4"/>
+      <c r="DC90" s="4"/>
     </row>
     <row r="91" spans="1:179" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="4" t="s">
@@ -17206,7 +17303,9 @@
       <c r="DB91" s="14">
         <v>122.50783516602633</v>
       </c>
-      <c r="DC91" s="20"/>
+      <c r="DC91" s="14">
+        <v>123.50114017624388</v>
+      </c>
       <c r="DD91" s="20"/>
       <c r="DE91" s="20"/>
       <c r="DF91" s="20"/>
@@ -17597,9 +17696,11 @@
         <v>138.87052204122486</v>
       </c>
       <c r="DB92" s="14">
-        <v>113.83023005825541</v>
-      </c>
-      <c r="DC92" s="20"/>
+        <v>113.83023005825545</v>
+      </c>
+      <c r="DC92" s="14">
+        <v>124.6332353511667</v>
+      </c>
       <c r="DD92" s="20"/>
       <c r="DE92" s="20"/>
       <c r="DF92" s="20"/>
@@ -17992,7 +18093,9 @@
       <c r="DB93" s="14">
         <v>120.15751852344485</v>
       </c>
-      <c r="DC93" s="20"/>
+      <c r="DC93" s="14">
+        <v>128.6772093800171</v>
+      </c>
       <c r="DD93" s="20"/>
       <c r="DE93" s="20"/>
       <c r="DF93" s="20"/>
@@ -18172,7 +18275,7 @@
       <c r="CZ94" s="8"/>
       <c r="DA94" s="8"/>
       <c r="DB94" s="8"/>
-      <c r="DC94" s="20"/>
+      <c r="DC94" s="8"/>
       <c r="DD94" s="20"/>
       <c r="DE94" s="20"/>
       <c r="DF94" s="20"/>
@@ -18563,9 +18666,11 @@
         <v>141.60762025518059</v>
       </c>
       <c r="DB95" s="14">
-        <v>117.07960867918344</v>
-      </c>
-      <c r="DC95" s="20"/>
+        <v>117.0659546021049</v>
+      </c>
+      <c r="DC95" s="14">
+        <v>124.51954236199391</v>
+      </c>
       <c r="DD95" s="20"/>
       <c r="DE95" s="20"/>
       <c r="DF95" s="20"/>
@@ -18746,6 +18851,7 @@
       <c r="CZ96" s="10"/>
       <c r="DA96" s="10"/>
       <c r="DB96" s="10"/>
+      <c r="DC96" s="10"/>
     </row>
     <row r="97" spans="1:179" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A97" s="11" t="s">
@@ -18856,6 +18962,7 @@
       <c r="CZ97" s="4"/>
       <c r="DA97" s="4"/>
       <c r="DB97" s="4"/>
+      <c r="DC97" s="4"/>
     </row>
     <row r="98" spans="1:179" x14ac:dyDescent="0.25">
       <c r="B98" s="4"/>
@@ -18963,6 +19070,7 @@
       <c r="CZ98" s="4"/>
       <c r="DA98" s="4"/>
       <c r="DB98" s="4"/>
+      <c r="DC98" s="4"/>
     </row>
     <row r="99" spans="1:179" x14ac:dyDescent="0.25">
       <c r="B99" s="4"/>
@@ -19070,6 +19178,7 @@
       <c r="CZ99" s="4"/>
       <c r="DA99" s="4"/>
       <c r="DB99" s="4"/>
+      <c r="DC99" s="4"/>
     </row>
     <row r="100" spans="1:179" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A100" s="4" t="s">
@@ -19180,6 +19289,7 @@
       <c r="CZ100" s="4"/>
       <c r="DA100" s="4"/>
       <c r="DB100" s="4"/>
+      <c r="DC100" s="4"/>
     </row>
     <row r="101" spans="1:179" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A101" s="4" t="s">
@@ -19290,10 +19400,11 @@
       <c r="CZ101" s="4"/>
       <c r="DA101" s="4"/>
       <c r="DB101" s="4"/>
+      <c r="DC101" s="4"/>
     </row>
     <row r="102" spans="1:179" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A102" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B102" s="4"/>
       <c r="C102" s="4"/>
@@ -19400,6 +19511,7 @@
       <c r="CZ102" s="4"/>
       <c r="DA102" s="4"/>
       <c r="DB102" s="4"/>
+      <c r="DC102" s="4"/>
     </row>
     <row r="103" spans="1:179" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A103" s="4"/>
@@ -19508,6 +19620,7 @@
       <c r="CZ103" s="4"/>
       <c r="DA103" s="4"/>
       <c r="DB103" s="4"/>
+      <c r="DC103" s="4"/>
     </row>
     <row r="104" spans="1:179" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A104" s="4" t="s">
@@ -19618,10 +19731,11 @@
       <c r="CZ104" s="4"/>
       <c r="DA104" s="4"/>
       <c r="DB104" s="4"/>
+      <c r="DC104" s="4"/>
     </row>
     <row r="105" spans="1:179" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A105" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B105" s="4"/>
       <c r="C105" s="4"/>
@@ -19728,6 +19842,7 @@
       <c r="CZ105" s="4"/>
       <c r="DA105" s="4"/>
       <c r="DB105" s="4"/>
+      <c r="DC105" s="4"/>
     </row>
     <row r="106" spans="1:179" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A106" s="4" t="s">
@@ -19838,6 +19953,7 @@
       <c r="CZ106" s="4"/>
       <c r="DA106" s="4"/>
       <c r="DB106" s="4"/>
+      <c r="DC106" s="4"/>
     </row>
     <row r="107" spans="1:179" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A107" s="4"/>
@@ -19946,6 +20062,7 @@
       <c r="CZ107" s="4"/>
       <c r="DA107" s="4"/>
       <c r="DB107" s="4"/>
+      <c r="DC107" s="4"/>
     </row>
     <row r="108" spans="1:179" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A108" s="15"/>
@@ -20108,6 +20225,7 @@
       <c r="DB108" s="24">
         <v>2026</v>
       </c>
+      <c r="DC108" s="24"/>
     </row>
     <row r="109" spans="1:179" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A109" s="5" t="s">
@@ -20427,6 +20545,9 @@
       </c>
       <c r="DB109" s="12" t="s">
         <v>2</v>
+      </c>
+      <c r="DC109" s="12" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="110" spans="1:179" s="18" customFormat="1" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -20536,6 +20657,7 @@
       <c r="CZ110" s="4"/>
       <c r="DA110" s="4"/>
       <c r="DB110" s="4"/>
+      <c r="DC110" s="4"/>
     </row>
     <row r="111" spans="1:179" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="4" t="s">
@@ -20854,9 +20976,11 @@
         <v>38.873313289402567</v>
       </c>
       <c r="DB111" s="14">
-        <v>35.516443405310717</v>
-      </c>
-      <c r="DC111" s="20"/>
+        <v>35.37132633454592</v>
+      </c>
+      <c r="DC111" s="14">
+        <v>22.107887995575652</v>
+      </c>
       <c r="DD111" s="20"/>
       <c r="DE111" s="20"/>
       <c r="DF111" s="20"/>
@@ -21247,9 +21371,11 @@
         <v>54.122131323881895</v>
       </c>
       <c r="DB112" s="14">
-        <v>59.553280997797216</v>
-      </c>
-      <c r="DC112" s="20"/>
+        <v>59.718542741960732</v>
+      </c>
+      <c r="DC112" s="14">
+        <v>74.348993769726036</v>
+      </c>
       <c r="DD112" s="20"/>
       <c r="DE112" s="20"/>
       <c r="DF112" s="20"/>
@@ -21640,9 +21766,11 @@
         <v>7.0045553867155288</v>
       </c>
       <c r="DB113" s="14">
-        <v>4.9302755968920673</v>
-      </c>
-      <c r="DC113" s="20"/>
+        <v>4.9101309234933472</v>
+      </c>
+      <c r="DC113" s="14">
+        <v>3.5431182346983192</v>
+      </c>
       <c r="DD113" s="20"/>
       <c r="DE113" s="20"/>
       <c r="DF113" s="20"/>
@@ -21822,7 +21950,7 @@
       <c r="CZ114" s="8"/>
       <c r="DA114" s="8"/>
       <c r="DB114" s="8"/>
-      <c r="DC114" s="20"/>
+      <c r="DC114" s="8"/>
       <c r="DD114" s="20"/>
       <c r="DE114" s="20"/>
       <c r="DF114" s="20"/>
@@ -22215,7 +22343,9 @@
       <c r="DB115" s="14">
         <v>100</v>
       </c>
-      <c r="DC115" s="20"/>
+      <c r="DC115" s="14">
+        <v>100</v>
+      </c>
       <c r="DD115" s="20"/>
       <c r="DE115" s="20"/>
       <c r="DF115" s="20"/>
@@ -22396,6 +22526,7 @@
       <c r="CZ116" s="10"/>
       <c r="DA116" s="10"/>
       <c r="DB116" s="10"/>
+      <c r="DC116" s="10"/>
     </row>
     <row r="117" spans="1:179" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A117" s="11" t="s">
@@ -22506,6 +22637,7 @@
       <c r="CZ117" s="4"/>
       <c r="DA117" s="4"/>
       <c r="DB117" s="4"/>
+      <c r="DC117" s="4"/>
     </row>
     <row r="118" spans="1:179" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B118" s="8"/>
@@ -22613,7 +22745,7 @@
       <c r="CZ118" s="8"/>
       <c r="DA118" s="8"/>
       <c r="DB118" s="8"/>
-      <c r="DC118" s="20"/>
+      <c r="DC118" s="8"/>
       <c r="DD118" s="20"/>
       <c r="DE118" s="20"/>
       <c r="DF118" s="20"/>
@@ -22793,7 +22925,7 @@
       <c r="CZ119" s="8"/>
       <c r="DA119" s="8"/>
       <c r="DB119" s="8"/>
-      <c r="DC119" s="20"/>
+      <c r="DC119" s="8"/>
       <c r="DD119" s="20"/>
       <c r="DE119" s="20"/>
       <c r="DF119" s="20"/>
@@ -22976,6 +23108,7 @@
       <c r="CZ120" s="4"/>
       <c r="DA120" s="4"/>
       <c r="DB120" s="4"/>
+      <c r="DC120" s="4"/>
     </row>
     <row r="121" spans="1:179" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A121" s="4" t="s">
@@ -23086,10 +23219,11 @@
       <c r="CZ121" s="4"/>
       <c r="DA121" s="4"/>
       <c r="DB121" s="4"/>
+      <c r="DC121" s="4"/>
     </row>
     <row r="122" spans="1:179" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A122" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B122" s="4"/>
       <c r="C122" s="4"/>
@@ -23196,6 +23330,7 @@
       <c r="CZ122" s="4"/>
       <c r="DA122" s="4"/>
       <c r="DB122" s="4"/>
+      <c r="DC122" s="4"/>
     </row>
     <row r="123" spans="1:179" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A123" s="4"/>
@@ -23304,6 +23439,7 @@
       <c r="CZ123" s="4"/>
       <c r="DA123" s="4"/>
       <c r="DB123" s="4"/>
+      <c r="DC123" s="4"/>
     </row>
     <row r="124" spans="1:179" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A124" s="4" t="s">
@@ -23414,10 +23550,11 @@
       <c r="CZ124" s="4"/>
       <c r="DA124" s="4"/>
       <c r="DB124" s="4"/>
+      <c r="DC124" s="4"/>
     </row>
     <row r="125" spans="1:179" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A125" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B125" s="4"/>
       <c r="C125" s="4"/>
@@ -23524,6 +23661,7 @@
       <c r="CZ125" s="4"/>
       <c r="DA125" s="4"/>
       <c r="DB125" s="4"/>
+      <c r="DC125" s="4"/>
     </row>
     <row r="126" spans="1:179" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A126" s="4" t="s">
@@ -23634,6 +23772,7 @@
       <c r="CZ126" s="4"/>
       <c r="DA126" s="4"/>
       <c r="DB126" s="4"/>
+      <c r="DC126" s="4"/>
     </row>
     <row r="127" spans="1:179" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A127" s="4"/>
@@ -23742,6 +23881,7 @@
       <c r="CZ127" s="4"/>
       <c r="DA127" s="4"/>
       <c r="DB127" s="4"/>
+      <c r="DC127" s="4"/>
     </row>
     <row r="128" spans="1:179" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A128" s="15"/>
@@ -23904,6 +24044,7 @@
       <c r="DB128" s="24">
         <v>2026</v>
       </c>
+      <c r="DC128" s="24"/>
     </row>
     <row r="129" spans="1:179" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A129" s="5" t="s">
@@ -24223,6 +24364,9 @@
       </c>
       <c r="DB129" s="12" t="s">
         <v>2</v>
+      </c>
+      <c r="DC129" s="12" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="130" spans="1:179" s="18" customFormat="1" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -24332,6 +24476,7 @@
       <c r="CZ130" s="4"/>
       <c r="DA130" s="4"/>
       <c r="DB130" s="4"/>
+      <c r="DC130" s="4"/>
     </row>
     <row r="131" spans="1:179" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A131" s="4" t="s">
@@ -24650,9 +24795,11 @@
         <v>38.202507532443192</v>
       </c>
       <c r="DB131" s="14">
-        <v>33.942737539478642</v>
-      </c>
-      <c r="DC131" s="20"/>
+        <v>33.800108191320845</v>
+      </c>
+      <c r="DC131" s="14">
+        <v>22.290191749410486</v>
+      </c>
       <c r="DD131" s="20"/>
       <c r="DE131" s="20"/>
       <c r="DF131" s="20"/>
@@ -25043,9 +25190,11 @@
         <v>55.188863030543864</v>
       </c>
       <c r="DB132" s="14">
-        <v>61.253278950725246</v>
-      </c>
-      <c r="DC132" s="20"/>
+        <v>61.416094915703979</v>
+      </c>
+      <c r="DC132" s="14">
+        <v>74.281171095301744</v>
+      </c>
       <c r="DD132" s="20"/>
       <c r="DE132" s="20"/>
       <c r="DF132" s="20"/>
@@ -25436,9 +25585,11 @@
         <v>6.6086294370129375</v>
       </c>
       <c r="DB133" s="14">
-        <v>4.8039835097961188</v>
-      </c>
-      <c r="DC133" s="20"/>
+        <v>4.7837968929751833</v>
+      </c>
+      <c r="DC133" s="14">
+        <v>3.428637155287769</v>
+      </c>
       <c r="DD133" s="20"/>
       <c r="DE133" s="20"/>
       <c r="DF133" s="20"/>
@@ -25618,7 +25769,7 @@
       <c r="CZ134" s="8"/>
       <c r="DA134" s="8"/>
       <c r="DB134" s="8"/>
-      <c r="DC134" s="20"/>
+      <c r="DC134" s="8"/>
       <c r="DD134" s="20"/>
       <c r="DE134" s="20"/>
       <c r="DF134" s="20"/>
@@ -26011,7 +26162,9 @@
       <c r="DB135" s="14">
         <v>100</v>
       </c>
-      <c r="DC135" s="20"/>
+      <c r="DC135" s="14">
+        <v>100</v>
+      </c>
       <c r="DD135" s="20"/>
       <c r="DE135" s="20"/>
       <c r="DF135" s="20"/>
@@ -26192,6 +26345,7 @@
       <c r="CZ136" s="10"/>
       <c r="DA136" s="10"/>
       <c r="DB136" s="10"/>
+      <c r="DC136" s="10"/>
     </row>
     <row r="137" spans="1:179" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A137" s="11" t="s">
@@ -26302,6 +26456,7 @@
       <c r="CZ137" s="4"/>
       <c r="DA137" s="4"/>
       <c r="DB137" s="4"/>
+      <c r="DC137" s="4"/>
     </row>
     <row r="138" spans="1:179" s="23" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A138" s="4"/>
@@ -26410,7 +26565,7 @@
       <c r="CZ138" s="13"/>
       <c r="DA138" s="13"/>
       <c r="DB138" s="13"/>
-      <c r="DC138" s="22"/>
+      <c r="DC138" s="13"/>
       <c r="DD138" s="22"/>
       <c r="DE138" s="22"/>
       <c r="DF138" s="22"/>
@@ -26492,6 +26647,8 @@
       <c r="CY139" s="30"/>
       <c r="CZ139" s="30"/>
       <c r="DA139" s="30"/>
+      <c r="DB139" s="30"/>
+      <c r="DC139" s="30"/>
     </row>
   </sheetData>
   <printOptions horizontalCentered="1"/>
@@ -26499,9 +26656,9 @@
   <pageSetup paperSize="9" scale="48" orientation="landscape" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
   <rowBreaks count="3" manualBreakCount="3">
-    <brk id="40" max="105" man="1"/>
-    <brk id="80" max="105" man="1"/>
-    <brk id="99" max="105" man="1"/>
+    <brk id="40" max="106" man="1"/>
+    <brk id="80" max="106" man="1"/>
+    <brk id="99" max="106" man="1"/>
   </rowBreaks>
 </worksheet>
 </file>